--- a/SOPs/Lab/general-filtering/templates/filtering-lab-data-sheets.xlsx
+++ b/SOPs/Lab/general-filtering/templates/filtering-lab-data-sheets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wampleka\Documents\Projects\WWS-standard-methods\SOPs\Lab\general-filtering\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50407A47-460E-4A7B-A50B-767E89E5F7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777A45AA-21E9-49EC-B1CB-AC35032B377D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FILL ME" sheetId="10" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
   <si>
     <t>Project</t>
   </si>
@@ -460,6 +460,9 @@
   <si>
     <t>Sample ID Type (choose one)</t>
   </si>
+  <si>
+    <t>For Many Sites Paste Site Names Here</t>
+  </si>
 </sst>
 </file>
 
@@ -801,9 +804,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -831,6 +831,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1263,91 +1264,97 @@
     <col min="1" max="1" width="39.7109375" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
     <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="37"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="36"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="31"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D3" s="41" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>42</v>
       </c>
       <c r="B4" s="31"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="32"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="31" t="str">
+        <f>_xlfn.TEXTJOIN(", ",TRUE,D4:D100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="31"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="33"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="32"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="32" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="32" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="38" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="38"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="37"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="34"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="33"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="34"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="33"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="35"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="34"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="14">
-        <f>COUNTA(_xlfn.TEXTSPLIT('FILL ME'!$B$5, ", "))</f>
+        <f>COUNTA(_xlfn.TEXTSPLIT('FILL ME'!#REF!, ", "))</f>
         <v>1</v>
       </c>
     </row>
@@ -1357,12 +1364,12 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
@@ -1373,28 +1380,28 @@
       <c r="D19" s="30"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1479,7 +1486,7 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D2" s="11" t="str">
@@ -1500,23 +1507,23 @@
       </c>
       <c r="H2" s="3" t="e" cm="1">
         <f t="array" ref="H2">_xlfn.LET(
-    _xlpm.items, _xlfn.TEXTSPLIT('FILL ME'!$B$5, ", "),
+    _xlpm.items, _xlfn.TEXTSPLIT('FILL ME'!#REF!, ", "),
     _xlpm.x, 'FILL ME'!$B$6,
     INDEX(_xlpm.items, ROUNDUP(_xlfn.SEQUENCE(COUNTA(_xlpm.items)*_xlpm.x)/_xlpm.x, 0))
 )</f>
-        <v>#VALUE!</v>
+        <v>#REF!</v>
       </c>
       <c r="I2" s="14" t="e">
         <f>CONCATENATE(H2,"_",TEXT(G2,"00"))</f>
-        <v>#VALUE!</v>
+        <v>#REF!</v>
       </c>
       <c r="J2" s="15" t="e">
         <f>CONCATENATE(C2,"_", H2,"_",D2,"_",TEXT(G2,"00"))</f>
-        <v>#VALUE!</v>
+        <v>#REF!</v>
       </c>
       <c r="K2" s="15" t="e">
         <f>CONCATENATE(C2,"_", H2,"_",TEXT(E2, "yyyymmdd"),"_",TEXT(F2, "hhmm"))</f>
-        <v>#VALUE!</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1529,7 +1536,7 @@
         <v/>
       </c>
       <c r="C3" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D3" s="11" t="str">
@@ -1567,7 +1574,7 @@
         <v/>
       </c>
       <c r="C4" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D4" s="11" t="str">
@@ -1605,7 +1612,7 @@
         <v/>
       </c>
       <c r="C5" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D5" s="11" t="str">
@@ -1643,7 +1650,7 @@
         <v/>
       </c>
       <c r="C6" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D6" s="11" t="str">
@@ -1681,7 +1688,7 @@
         <v/>
       </c>
       <c r="C7" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D7" s="11" t="str">
@@ -1719,7 +1726,7 @@
         <v/>
       </c>
       <c r="C8" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D8" s="11" t="str">
@@ -1757,7 +1764,7 @@
         <v/>
       </c>
       <c r="C9" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D9" s="11" t="str">
@@ -1795,7 +1802,7 @@
         <v/>
       </c>
       <c r="C10" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D10" s="11" t="str">
@@ -1833,7 +1840,7 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D11" s="11" t="str">
@@ -1871,7 +1878,7 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D12" s="11" t="str">
@@ -1909,7 +1916,7 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D13" s="11" t="str">
@@ -1947,7 +1954,7 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D14" s="11" t="str">
@@ -1985,7 +1992,7 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D15" s="11" t="str">
@@ -2023,7 +2030,7 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D16" s="11" t="str">
@@ -2061,7 +2068,7 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D17" s="11" t="str">
@@ -2099,7 +2106,7 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D18" s="11" t="str">
@@ -2137,7 +2144,7 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D19" s="11" t="str">
@@ -2175,7 +2182,7 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D20" s="11" t="str">
@@ -2213,7 +2220,7 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D21" s="11" t="str">
@@ -2251,7 +2258,7 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D22" s="11" t="str">
@@ -2289,7 +2296,7 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D23" s="11" t="str">
@@ -2327,7 +2334,7 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D24" s="11" t="str">
@@ -2365,7 +2372,7 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D25" s="11" t="str">
@@ -2403,7 +2410,7 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D26" s="11" t="str">
@@ -2441,7 +2448,7 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D27" s="11" t="str">
@@ -2479,7 +2486,7 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D28" s="11" t="str">
@@ -2517,7 +2524,7 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D29" s="11" t="str">
@@ -2555,7 +2562,7 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D30" s="11" t="str">
@@ -2593,7 +2600,7 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D31" s="11" t="str">
@@ -2631,7 +2638,7 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D32" s="11" t="str">
@@ -2669,7 +2676,7 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D33" s="11" t="str">
@@ -2707,7 +2714,7 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D34" s="11" t="str">
@@ -2745,7 +2752,7 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D35" s="11" t="str">
@@ -2783,7 +2790,7 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D36" s="11" t="str">
@@ -2821,7 +2828,7 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D37" s="11" t="str">
@@ -2859,7 +2866,7 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D38" s="11" t="str">
@@ -2897,7 +2904,7 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D39" s="11" t="str">
@@ -2935,7 +2942,7 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D40" s="11" t="str">
@@ -2973,7 +2980,7 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D41" s="11" t="str">
@@ -3011,7 +3018,7 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D42" s="11" t="str">
@@ -3049,7 +3056,7 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D43" s="11" t="str">
@@ -3087,7 +3094,7 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D44" s="11" t="str">
@@ -3125,7 +3132,7 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D45" s="11" t="str">
@@ -3163,7 +3170,7 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D46" s="11" t="str">
@@ -3201,7 +3208,7 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D47" s="11" t="str">
@@ -3239,7 +3246,7 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D48" s="11" t="str">
@@ -3277,7 +3284,7 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D49" s="11" t="str">
@@ -3315,7 +3322,7 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D50" s="11" t="str">
@@ -3354,7 +3361,7 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D51" s="11" t="str">
@@ -3393,7 +3400,7 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D52" s="11" t="str">
@@ -3432,7 +3439,7 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D53" s="11" t="str">
@@ -3471,7 +3478,7 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D54" s="11" t="str">
@@ -3510,7 +3517,7 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D55" s="11" t="str">
@@ -3549,7 +3556,7 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D56" s="11" t="str">
@@ -3588,7 +3595,7 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D57" s="11" t="str">
@@ -3627,7 +3634,7 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D58" s="11" t="str">
@@ -3666,7 +3673,7 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D59" s="11" t="str">
@@ -3705,7 +3712,7 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D60" s="11" t="str">
@@ -3744,7 +3751,7 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D61" s="11" t="str">
@@ -3779,7 +3786,7 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D62" s="11" t="str">
@@ -3814,7 +3821,7 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D63" s="11" t="str">
@@ -3849,7 +3856,7 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D64" s="11" t="str">
@@ -3884,7 +3891,7 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D65" s="11" t="str">
@@ -3919,7 +3926,7 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D66" s="11" t="str">
@@ -3954,7 +3961,7 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D67" s="11" t="str">
@@ -3989,7 +3996,7 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D68" s="11" t="str">
@@ -4024,7 +4031,7 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D69" s="11" t="str">
@@ -4059,7 +4066,7 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D70" s="11" t="str">
@@ -4094,7 +4101,7 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D71" s="11" t="str">
@@ -4129,7 +4136,7 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D72" s="11" t="str">
@@ -4164,7 +4171,7 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D73" s="11" t="str">
@@ -4199,7 +4206,7 @@
         <v/>
       </c>
       <c r="C74" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D74" s="11" t="str">
@@ -4234,7 +4241,7 @@
         <v/>
       </c>
       <c r="C75" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D75" s="11" t="str">
@@ -4269,7 +4276,7 @@
         <v/>
       </c>
       <c r="C76" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D76" s="11" t="str">
@@ -4304,7 +4311,7 @@
         <v/>
       </c>
       <c r="C77" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D77" s="11" t="str">
@@ -4339,7 +4346,7 @@
         <v/>
       </c>
       <c r="C78" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D78" s="11" t="str">
@@ -4374,7 +4381,7 @@
         <v/>
       </c>
       <c r="C79" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D79" s="11" t="str">
@@ -4409,7 +4416,7 @@
         <v/>
       </c>
       <c r="C80" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D80" s="11" t="str">
@@ -4444,7 +4451,7 @@
         <v/>
       </c>
       <c r="C81" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D81" s="11" t="str">
@@ -4479,7 +4486,7 @@
         <v/>
       </c>
       <c r="C82" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D82" s="11" t="str">
@@ -4514,7 +4521,7 @@
         <v/>
       </c>
       <c r="C83" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D83" s="11" t="str">
@@ -4549,7 +4556,7 @@
         <v/>
       </c>
       <c r="C84" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D84" s="11" t="str">
@@ -4584,7 +4591,7 @@
         <v/>
       </c>
       <c r="C85" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D85" s="11" t="str">
@@ -4619,7 +4626,7 @@
         <v/>
       </c>
       <c r="C86" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D86" s="11" t="str">
@@ -4654,7 +4661,7 @@
         <v/>
       </c>
       <c r="C87" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D87" s="11" t="str">
@@ -4689,7 +4696,7 @@
         <v/>
       </c>
       <c r="C88" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D88" s="11" t="str">
@@ -4724,7 +4731,7 @@
         <v/>
       </c>
       <c r="C89" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D89" s="11" t="str">
@@ -4759,7 +4766,7 @@
         <v/>
       </c>
       <c r="C90" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D90" s="11" t="str">
@@ -4794,7 +4801,7 @@
         <v/>
       </c>
       <c r="C91" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D91" s="11" t="str">
@@ -4829,7 +4836,7 @@
         <v/>
       </c>
       <c r="C92" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D92" s="11" t="str">
@@ -4864,7 +4871,7 @@
         <v/>
       </c>
       <c r="C93" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D93" s="11" t="str">
@@ -4899,7 +4906,7 @@
         <v/>
       </c>
       <c r="C94" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D94" s="11" t="str">
@@ -4934,7 +4941,7 @@
         <v/>
       </c>
       <c r="C95" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D95" s="11" t="str">
@@ -4969,7 +4976,7 @@
         <v/>
       </c>
       <c r="C96" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D96" s="11" t="str">
@@ -5004,7 +5011,7 @@
         <v/>
       </c>
       <c r="C97" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D97" s="11" t="str">
@@ -5039,7 +5046,7 @@
         <v/>
       </c>
       <c r="C98" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D98" s="11" t="str">
@@ -5074,7 +5081,7 @@
         <v/>
       </c>
       <c r="C99" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D99" s="11" t="str">
@@ -5109,7 +5116,7 @@
         <v/>
       </c>
       <c r="C100" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D100" s="11" t="str">
@@ -5144,7 +5151,7 @@
         <v/>
       </c>
       <c r="C101" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D101" s="11" t="str">
@@ -5179,7 +5186,7 @@
         <v/>
       </c>
       <c r="C102" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D102" s="11" t="str">
@@ -5214,7 +5221,7 @@
         <v/>
       </c>
       <c r="C103" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D103" s="11" t="str">
@@ -5249,7 +5256,7 @@
         <v/>
       </c>
       <c r="C104" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D104" s="11" t="str">
@@ -5284,7 +5291,7 @@
         <v/>
       </c>
       <c r="C105" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D105" s="11" t="str">
@@ -5316,7 +5323,7 @@
         <v/>
       </c>
       <c r="C106" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D106" s="11" t="str">
@@ -5348,7 +5355,7 @@
         <v/>
       </c>
       <c r="C107" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D107" s="11" t="str">
@@ -5380,7 +5387,7 @@
         <v/>
       </c>
       <c r="C108" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D108" s="11" t="str">
@@ -5412,7 +5419,7 @@
         <v/>
       </c>
       <c r="C109" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D109" s="11" t="str">
@@ -5444,7 +5451,7 @@
         <v/>
       </c>
       <c r="C110" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D110" s="11" t="str">
@@ -5476,7 +5483,7 @@
         <v/>
       </c>
       <c r="C111" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D111" s="11" t="str">
@@ -5508,7 +5515,7 @@
         <v/>
       </c>
       <c r="C112" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D112" s="11" t="str">
@@ -5540,7 +5547,7 @@
         <v/>
       </c>
       <c r="C113" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D113" s="11" t="str">
@@ -5572,7 +5579,7 @@
         <v/>
       </c>
       <c r="C114" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D114" s="11" t="str">
@@ -5604,7 +5611,7 @@
         <v/>
       </c>
       <c r="C115" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D115" s="11" t="str">
@@ -5636,7 +5643,7 @@
         <v/>
       </c>
       <c r="C116" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D116" s="11" t="str">
@@ -5668,7 +5675,7 @@
         <v/>
       </c>
       <c r="C117" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D117" s="11" t="str">
@@ -5700,7 +5707,7 @@
         <v/>
       </c>
       <c r="C118" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D118" s="11" t="str">
@@ -5732,7 +5739,7 @@
         <v/>
       </c>
       <c r="C119" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D119" s="11" t="str">
@@ -5764,7 +5771,7 @@
         <v/>
       </c>
       <c r="C120" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D120" s="11" t="str">
@@ -5796,7 +5803,7 @@
         <v/>
       </c>
       <c r="C121" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D121" s="11" t="str">
@@ -5828,7 +5835,7 @@
         <v/>
       </c>
       <c r="C122" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D122" s="11" t="str">
@@ -5860,7 +5867,7 @@
         <v/>
       </c>
       <c r="C123" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D123" s="11" t="str">
@@ -5892,7 +5899,7 @@
         <v/>
       </c>
       <c r="C124" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D124" s="11" t="str">
@@ -5924,7 +5931,7 @@
         <v/>
       </c>
       <c r="C125" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D125" s="11" t="str">
@@ -5956,7 +5963,7 @@
         <v/>
       </c>
       <c r="C126" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D126" s="11" t="str">
@@ -5988,7 +5995,7 @@
         <v/>
       </c>
       <c r="C127" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D127" s="11" t="str">
@@ -6020,7 +6027,7 @@
         <v/>
       </c>
       <c r="C128" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D128" s="11" t="str">
@@ -6052,7 +6059,7 @@
         <v/>
       </c>
       <c r="C129" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D129" s="11" t="str">
@@ -6084,7 +6091,7 @@
         <v/>
       </c>
       <c r="C130" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D130" s="11" t="str">
@@ -6116,7 +6123,7 @@
         <v/>
       </c>
       <c r="C131" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D131" s="11" t="str">
@@ -6148,7 +6155,7 @@
         <v/>
       </c>
       <c r="C132" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D132" s="11" t="str">
@@ -6180,7 +6187,7 @@
         <v/>
       </c>
       <c r="C133" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D133" s="11" t="str">
@@ -6212,7 +6219,7 @@
         <v/>
       </c>
       <c r="C134" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D134" s="11" t="str">
@@ -6244,7 +6251,7 @@
         <v/>
       </c>
       <c r="C135" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D135" s="11" t="str">
@@ -6276,7 +6283,7 @@
         <v/>
       </c>
       <c r="C136" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D136" s="11" t="str">
@@ -6308,7 +6315,7 @@
         <v/>
       </c>
       <c r="C137" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D137" s="11" t="str">
@@ -6340,7 +6347,7 @@
         <v/>
       </c>
       <c r="C138" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D138" s="11" t="str">
@@ -6372,7 +6379,7 @@
         <v/>
       </c>
       <c r="C139" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D139" s="11" t="str">
@@ -6404,7 +6411,7 @@
         <v/>
       </c>
       <c r="C140" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D140" s="11" t="str">
@@ -6436,7 +6443,7 @@
         <v/>
       </c>
       <c r="C141" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D141" s="11" t="str">
@@ -6468,7 +6475,7 @@
         <v/>
       </c>
       <c r="C142" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D142" s="11" t="str">
@@ -6500,7 +6507,7 @@
         <v/>
       </c>
       <c r="C143" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D143" s="11" t="str">
@@ -6532,7 +6539,7 @@
         <v/>
       </c>
       <c r="C144" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D144" s="11" t="str">
@@ -6564,7 +6571,7 @@
         <v/>
       </c>
       <c r="C145" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D145" s="11" t="str">
@@ -6596,7 +6603,7 @@
         <v/>
       </c>
       <c r="C146" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D146" s="11" t="str">
@@ -6628,7 +6635,7 @@
         <v/>
       </c>
       <c r="C147" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D147" s="11" t="str">
@@ -6660,7 +6667,7 @@
         <v/>
       </c>
       <c r="C148" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D148" s="11" t="str">
@@ -6692,7 +6699,7 @@
         <v/>
       </c>
       <c r="C149" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D149" s="11" t="str">
@@ -6724,7 +6731,7 @@
         <v/>
       </c>
       <c r="C150" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D150" s="11" t="str">
@@ -6756,7 +6763,7 @@
         <v/>
       </c>
       <c r="C151" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D151" s="11" t="str">
@@ -6788,7 +6795,7 @@
         <v/>
       </c>
       <c r="C152" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D152" s="11" t="str">
@@ -6820,7 +6827,7 @@
         <v/>
       </c>
       <c r="C153" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D153" s="11" t="str">
@@ -6852,7 +6859,7 @@
         <v/>
       </c>
       <c r="C154" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D154" s="11" t="str">
@@ -6884,7 +6891,7 @@
         <v/>
       </c>
       <c r="C155" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D155" s="11" t="str">
@@ -6916,7 +6923,7 @@
         <v/>
       </c>
       <c r="C156" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D156" s="11" t="str">
@@ -6948,7 +6955,7 @@
         <v/>
       </c>
       <c r="C157" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D157" s="11" t="str">
@@ -6980,7 +6987,7 @@
         <v/>
       </c>
       <c r="C158" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D158" s="11" t="str">
@@ -7012,7 +7019,7 @@
         <v/>
       </c>
       <c r="C159" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D159" s="11" t="str">
@@ -7044,7 +7051,7 @@
         <v/>
       </c>
       <c r="C160" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D160" s="11" t="str">
@@ -7076,7 +7083,7 @@
         <v/>
       </c>
       <c r="C161" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D161" s="11" t="str">
@@ -7108,7 +7115,7 @@
         <v/>
       </c>
       <c r="C162" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D162" s="11" t="str">
@@ -7140,7 +7147,7 @@
         <v/>
       </c>
       <c r="C163" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D163" s="11" t="str">
@@ -7172,7 +7179,7 @@
         <v/>
       </c>
       <c r="C164" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D164" s="11" t="str">
@@ -7204,7 +7211,7 @@
         <v/>
       </c>
       <c r="C165" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D165" s="11" t="str">
@@ -7236,7 +7243,7 @@
         <v/>
       </c>
       <c r="C166" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D166" s="11" t="str">
@@ -7268,7 +7275,7 @@
         <v/>
       </c>
       <c r="C167" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D167" s="11" t="str">
@@ -7300,7 +7307,7 @@
         <v/>
       </c>
       <c r="C168" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D168" s="11" t="str">
@@ -7332,7 +7339,7 @@
         <v/>
       </c>
       <c r="C169" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D169" s="11" t="str">
@@ -7364,7 +7371,7 @@
         <v/>
       </c>
       <c r="C170" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D170" s="11" t="str">
@@ -7396,7 +7403,7 @@
         <v/>
       </c>
       <c r="C171" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D171" s="11" t="str">
@@ -7428,7 +7435,7 @@
         <v/>
       </c>
       <c r="C172" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D172" s="11" t="str">
@@ -7460,7 +7467,7 @@
         <v/>
       </c>
       <c r="C173" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D173" s="11" t="str">
@@ -7492,7 +7499,7 @@
         <v/>
       </c>
       <c r="C174" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D174" s="11" t="str">
@@ -7524,7 +7531,7 @@
         <v/>
       </c>
       <c r="C175" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D175" s="11" t="str">
@@ -7556,7 +7563,7 @@
         <v/>
       </c>
       <c r="C176" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D176" s="11" t="str">
@@ -7588,7 +7595,7 @@
         <v/>
       </c>
       <c r="C177" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D177" s="11" t="str">
@@ -7620,7 +7627,7 @@
         <v/>
       </c>
       <c r="C178" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D178" s="11" t="str">
@@ -7652,7 +7659,7 @@
         <v/>
       </c>
       <c r="C179" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D179" s="11" t="str">
@@ -7684,7 +7691,7 @@
         <v/>
       </c>
       <c r="C180" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D180" s="11" t="str">
@@ -7716,7 +7723,7 @@
         <v/>
       </c>
       <c r="C181" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D181" s="11" t="str">
@@ -7748,7 +7755,7 @@
         <v/>
       </c>
       <c r="C182" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D182" s="11" t="str">
@@ -7780,7 +7787,7 @@
         <v/>
       </c>
       <c r="C183" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D183" s="11" t="str">
@@ -7812,7 +7819,7 @@
         <v/>
       </c>
       <c r="C184" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D184" s="11" t="str">
@@ -7844,7 +7851,7 @@
         <v/>
       </c>
       <c r="C185" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D185" s="11" t="str">
@@ -7876,7 +7883,7 @@
         <v/>
       </c>
       <c r="C186" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D186" s="11" t="str">
@@ -7908,7 +7915,7 @@
         <v/>
       </c>
       <c r="C187" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D187" s="11" t="str">
@@ -7940,7 +7947,7 @@
         <v/>
       </c>
       <c r="C188" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D188" s="11" t="str">
@@ -7972,7 +7979,7 @@
         <v/>
       </c>
       <c r="C189" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D189" s="11" t="str">
@@ -8004,7 +8011,7 @@
         <v/>
       </c>
       <c r="C190" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D190" s="11" t="str">
@@ -8036,7 +8043,7 @@
         <v/>
       </c>
       <c r="C191" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D191" s="11" t="str">
@@ -8068,7 +8075,7 @@
         <v/>
       </c>
       <c r="C192" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D192" s="11" t="str">
@@ -8100,7 +8107,7 @@
         <v/>
       </c>
       <c r="C193" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D193" s="11" t="str">
@@ -8132,7 +8139,7 @@
         <v/>
       </c>
       <c r="C194" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D194" s="11" t="str">
@@ -8164,7 +8171,7 @@
         <v/>
       </c>
       <c r="C195" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D195" s="11" t="str">
@@ -8196,7 +8203,7 @@
         <v/>
       </c>
       <c r="C196" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D196" s="11" t="str">
@@ -8228,7 +8235,7 @@
         <v/>
       </c>
       <c r="C197" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D197" s="11" t="str">
@@ -8260,7 +8267,7 @@
         <v/>
       </c>
       <c r="C198" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D198" s="11" t="str">
@@ -8292,7 +8299,7 @@
         <v/>
       </c>
       <c r="C199" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D199" s="11" t="str">
@@ -8324,7 +8331,7 @@
         <v/>
       </c>
       <c r="C200" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D200" s="11" t="str">
@@ -8356,7 +8363,7 @@
         <v/>
       </c>
       <c r="C201" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D201" s="11" t="str">
@@ -8388,7 +8395,7 @@
         <v/>
       </c>
       <c r="C202" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D202" s="11" t="str">
@@ -8420,7 +8427,7 @@
         <v/>
       </c>
       <c r="C203" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D203" s="11" t="str">
@@ -8452,7 +8459,7 @@
         <v/>
       </c>
       <c r="C204" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D204" s="11" t="str">
@@ -8484,7 +8491,7 @@
         <v/>
       </c>
       <c r="C205" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D205" s="11" t="str">
@@ -8516,7 +8523,7 @@
         <v/>
       </c>
       <c r="C206" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D206" s="11" t="str">
@@ -8548,7 +8555,7 @@
         <v/>
       </c>
       <c r="C207" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D207" s="11" t="str">
@@ -8580,7 +8587,7 @@
         <v/>
       </c>
       <c r="C208" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D208" s="11" t="str">
@@ -8612,7 +8619,7 @@
         <v/>
       </c>
       <c r="C209" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D209" s="11" t="str">
@@ -8644,7 +8651,7 @@
         <v/>
       </c>
       <c r="C210" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D210" s="11" t="str">
@@ -8676,7 +8683,7 @@
         <v/>
       </c>
       <c r="C211" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D211" s="11" t="str">
@@ -8708,7 +8715,7 @@
         <v/>
       </c>
       <c r="C212" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D212" s="11" t="str">
@@ -8740,7 +8747,7 @@
         <v/>
       </c>
       <c r="C213" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D213" s="11" t="str">
@@ -8772,7 +8779,7 @@
         <v/>
       </c>
       <c r="C214" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D214" s="11" t="str">
@@ -8804,7 +8811,7 @@
         <v/>
       </c>
       <c r="C215" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D215" s="11" t="str">
@@ -8836,7 +8843,7 @@
         <v/>
       </c>
       <c r="C216" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D216" s="11" t="str">
@@ -8868,7 +8875,7 @@
         <v/>
       </c>
       <c r="C217" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D217" s="11" t="str">
@@ -8900,7 +8907,7 @@
         <v/>
       </c>
       <c r="C218" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D218" s="11" t="str">
@@ -8932,7 +8939,7 @@
         <v/>
       </c>
       <c r="C219" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D219" s="11" t="str">
@@ -8964,7 +8971,7 @@
         <v/>
       </c>
       <c r="C220" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D220" s="11" t="str">
@@ -8996,7 +9003,7 @@
         <v/>
       </c>
       <c r="C221" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D221" s="11" t="str">
@@ -9028,7 +9035,7 @@
         <v/>
       </c>
       <c r="C222" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D222" s="11" t="str">
@@ -9060,7 +9067,7 @@
         <v/>
       </c>
       <c r="C223" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D223" s="11" t="str">
@@ -9092,7 +9099,7 @@
         <v/>
       </c>
       <c r="C224" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D224" s="11" t="str">
@@ -9124,7 +9131,7 @@
         <v/>
       </c>
       <c r="C225" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D225" s="11" t="str">
@@ -9156,7 +9163,7 @@
         <v/>
       </c>
       <c r="C226" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D226" s="11" t="str">
@@ -9188,7 +9195,7 @@
         <v/>
       </c>
       <c r="C227" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D227" s="11" t="str">
@@ -9220,7 +9227,7 @@
         <v/>
       </c>
       <c r="C228" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D228" s="11" t="str">
@@ -9252,7 +9259,7 @@
         <v/>
       </c>
       <c r="C229" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D229" s="11" t="str">
@@ -9284,7 +9291,7 @@
         <v/>
       </c>
       <c r="C230" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D230" s="11" t="str">
@@ -9316,7 +9323,7 @@
         <v/>
       </c>
       <c r="C231" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D231" s="11" t="str">
@@ -9348,7 +9355,7 @@
         <v/>
       </c>
       <c r="C232" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D232" s="11" t="str">
@@ -9380,7 +9387,7 @@
         <v/>
       </c>
       <c r="C233" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D233" s="11" t="str">
@@ -9412,7 +9419,7 @@
         <v/>
       </c>
       <c r="C234" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D234" s="11" t="str">
@@ -9444,7 +9451,7 @@
         <v/>
       </c>
       <c r="C235" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D235" s="11" t="str">
@@ -9476,7 +9483,7 @@
         <v/>
       </c>
       <c r="C236" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D236" s="11" t="str">
@@ -9508,7 +9515,7 @@
         <v/>
       </c>
       <c r="C237" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D237" s="11" t="str">
@@ -9540,7 +9547,7 @@
         <v/>
       </c>
       <c r="C238" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D238" s="11" t="str">
@@ -9572,7 +9579,7 @@
         <v/>
       </c>
       <c r="C239" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D239" s="11" t="str">
@@ -9604,7 +9611,7 @@
         <v/>
       </c>
       <c r="C240" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D240" s="11" t="str">
@@ -9636,7 +9643,7 @@
         <v/>
       </c>
       <c r="C241" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D241" s="11" t="str">
@@ -9668,7 +9675,7 @@
         <v/>
       </c>
       <c r="C242" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D242" s="11" t="str">
@@ -9700,7 +9707,7 @@
         <v/>
       </c>
       <c r="C243" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D243" s="11" t="str">
@@ -9732,7 +9739,7 @@
         <v/>
       </c>
       <c r="C244" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D244" s="11" t="str">
@@ -9764,7 +9771,7 @@
         <v/>
       </c>
       <c r="C245" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D245" s="11" t="str">
@@ -9796,7 +9803,7 @@
         <v/>
       </c>
       <c r="C246" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D246" s="11" t="str">
@@ -9828,7 +9835,7 @@
         <v/>
       </c>
       <c r="C247" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D247" s="11" t="str">
@@ -9860,7 +9867,7 @@
         <v/>
       </c>
       <c r="C248" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D248" s="11" t="str">
@@ -9892,7 +9899,7 @@
         <v/>
       </c>
       <c r="C249" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D249" s="11" t="str">
@@ -9924,7 +9931,7 @@
         <v/>
       </c>
       <c r="C250" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D250" s="11" t="str">
@@ -9956,7 +9963,7 @@
         <v/>
       </c>
       <c r="C251" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D251" s="11" t="str">
@@ -9988,7 +9995,7 @@
         <v/>
       </c>
       <c r="C252" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D252" s="11" t="str">
@@ -10020,7 +10027,7 @@
         <v/>
       </c>
       <c r="C253" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D253" s="11" t="str">
@@ -10052,7 +10059,7 @@
         <v/>
       </c>
       <c r="C254" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D254" s="11" t="str">
@@ -10084,7 +10091,7 @@
         <v/>
       </c>
       <c r="C255" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D255" s="11" t="str">
@@ -10116,7 +10123,7 @@
         <v/>
       </c>
       <c r="C256" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D256" s="11" t="str">
@@ -10148,7 +10155,7 @@
         <v/>
       </c>
       <c r="C257" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D257" s="11" t="str">
@@ -10180,7 +10187,7 @@
         <v/>
       </c>
       <c r="C258" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D258" s="11" t="str">
@@ -10212,7 +10219,7 @@
         <v/>
       </c>
       <c r="C259" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D259" s="11" t="str">
@@ -10244,7 +10251,7 @@
         <v/>
       </c>
       <c r="C260" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D260" s="11" t="str">
@@ -10276,7 +10283,7 @@
         <v/>
       </c>
       <c r="C261" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D261" s="11" t="str">
@@ -10308,7 +10315,7 @@
         <v/>
       </c>
       <c r="C262" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D262" s="11" t="str">
@@ -10340,7 +10347,7 @@
         <v/>
       </c>
       <c r="C263" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D263" s="11" t="str">
@@ -10372,7 +10379,7 @@
         <v/>
       </c>
       <c r="C264" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D264" s="11" t="str">
@@ -10404,7 +10411,7 @@
         <v/>
       </c>
       <c r="C265" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D265" s="11" t="str">
@@ -10436,7 +10443,7 @@
         <v/>
       </c>
       <c r="C266" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D266" s="11" t="str">
@@ -10468,7 +10475,7 @@
         <v/>
       </c>
       <c r="C267" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D267" s="11" t="str">
@@ -10500,7 +10507,7 @@
         <v/>
       </c>
       <c r="C268" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D268" s="11" t="str">
@@ -10532,7 +10539,7 @@
         <v/>
       </c>
       <c r="C269" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D269" s="11" t="str">
@@ -10564,7 +10571,7 @@
         <v/>
       </c>
       <c r="C270" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D270" s="11" t="str">
@@ -10596,7 +10603,7 @@
         <v/>
       </c>
       <c r="C271" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D271" s="11" t="str">
@@ -10628,7 +10635,7 @@
         <v/>
       </c>
       <c r="C272" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D272" s="11" t="str">
@@ -10660,7 +10667,7 @@
         <v/>
       </c>
       <c r="C273" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D273" s="11" t="str">
@@ -10692,7 +10699,7 @@
         <v/>
       </c>
       <c r="C274" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D274" s="11" t="str">
@@ -10724,7 +10731,7 @@
         <v/>
       </c>
       <c r="C275" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D275" s="11" t="str">
@@ -10756,7 +10763,7 @@
         <v/>
       </c>
       <c r="C276" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D276" s="11" t="str">
@@ -10788,7 +10795,7 @@
         <v/>
       </c>
       <c r="C277" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D277" s="11" t="str">
@@ -10820,7 +10827,7 @@
         <v/>
       </c>
       <c r="C278" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D278" s="11" t="str">
@@ -10852,7 +10859,7 @@
         <v/>
       </c>
       <c r="C279" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D279" s="11" t="str">
@@ -10884,7 +10891,7 @@
         <v/>
       </c>
       <c r="C280" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D280" s="11" t="str">
@@ -10916,7 +10923,7 @@
         <v/>
       </c>
       <c r="C281" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D281" s="11" t="str">
@@ -10948,7 +10955,7 @@
         <v/>
       </c>
       <c r="C282" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D282" s="11" t="str">
@@ -10980,7 +10987,7 @@
         <v/>
       </c>
       <c r="C283" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D283" s="11" t="str">
@@ -11012,7 +11019,7 @@
         <v/>
       </c>
       <c r="C284" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D284" s="11" t="str">
@@ -11044,7 +11051,7 @@
         <v/>
       </c>
       <c r="C285" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D285" s="11" t="str">
@@ -11076,7 +11083,7 @@
         <v/>
       </c>
       <c r="C286" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D286" s="11" t="str">
@@ -11108,7 +11115,7 @@
         <v/>
       </c>
       <c r="C287" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D287" s="11" t="str">
@@ -11140,7 +11147,7 @@
         <v/>
       </c>
       <c r="C288" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D288" s="11" t="str">
@@ -11172,7 +11179,7 @@
         <v/>
       </c>
       <c r="C289" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D289" s="11" t="str">
@@ -11204,7 +11211,7 @@
         <v/>
       </c>
       <c r="C290" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D290" s="11" t="str">
@@ -11236,7 +11243,7 @@
         <v/>
       </c>
       <c r="C291" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D291" s="11" t="str">
@@ -11268,7 +11275,7 @@
         <v/>
       </c>
       <c r="C292" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D292" s="11" t="str">
@@ -11300,7 +11307,7 @@
         <v/>
       </c>
       <c r="C293" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D293" s="11" t="str">
@@ -11332,7 +11339,7 @@
         <v/>
       </c>
       <c r="C294" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D294" s="11" t="str">
@@ -11364,7 +11371,7 @@
         <v/>
       </c>
       <c r="C295" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D295" s="11" t="str">
@@ -11396,7 +11403,7 @@
         <v/>
       </c>
       <c r="C296" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D296" s="11" t="str">
@@ -11428,7 +11435,7 @@
         <v/>
       </c>
       <c r="C297" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D297" s="11" t="str">
@@ -11460,7 +11467,7 @@
         <v/>
       </c>
       <c r="C298" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D298" s="11" t="str">
@@ -11492,7 +11499,7 @@
         <v/>
       </c>
       <c r="C299" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D299" s="11" t="str">
@@ -11524,7 +11531,7 @@
         <v/>
       </c>
       <c r="C300" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D300" s="11" t="str">
@@ -11556,7 +11563,7 @@
         <v/>
       </c>
       <c r="C301" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D301" s="11" t="str">
@@ -11588,7 +11595,7 @@
         <v/>
       </c>
       <c r="C302" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D302" s="11" t="str">
@@ -11620,7 +11627,7 @@
         <v/>
       </c>
       <c r="C303" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D303" s="11" t="str">
@@ -11652,7 +11659,7 @@
         <v/>
       </c>
       <c r="C304" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D304" s="11" t="str">
@@ -11684,7 +11691,7 @@
         <v/>
       </c>
       <c r="C305" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D305" s="11" t="str">
@@ -11716,7 +11723,7 @@
         <v/>
       </c>
       <c r="C306" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D306" s="11" t="str">
@@ -11748,7 +11755,7 @@
         <v/>
       </c>
       <c r="C307" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D307" s="11" t="str">
@@ -11780,7 +11787,7 @@
         <v/>
       </c>
       <c r="C308" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D308" s="11" t="str">
@@ -11812,7 +11819,7 @@
         <v/>
       </c>
       <c r="C309" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D309" s="11" t="str">
@@ -11844,7 +11851,7 @@
         <v/>
       </c>
       <c r="C310" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D310" s="11" t="str">
@@ -11876,7 +11883,7 @@
         <v/>
       </c>
       <c r="C311" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D311" s="11" t="str">
@@ -11908,7 +11915,7 @@
         <v/>
       </c>
       <c r="C312" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D312" s="11" t="str">
@@ -11940,7 +11947,7 @@
         <v/>
       </c>
       <c r="C313" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D313" s="11" t="str">
@@ -11972,7 +11979,7 @@
         <v/>
       </c>
       <c r="C314" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D314" s="11" t="str">
@@ -12004,7 +12011,7 @@
         <v/>
       </c>
       <c r="C315" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D315" s="11" t="str">
@@ -12036,7 +12043,7 @@
         <v/>
       </c>
       <c r="C316" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D316" s="11" t="str">
@@ -12068,7 +12075,7 @@
         <v/>
       </c>
       <c r="C317" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D317" s="11" t="str">
@@ -12100,7 +12107,7 @@
         <v/>
       </c>
       <c r="C318" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D318" s="11" t="str">
@@ -12132,7 +12139,7 @@
         <v/>
       </c>
       <c r="C319" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D319" s="11" t="str">
@@ -12164,7 +12171,7 @@
         <v/>
       </c>
       <c r="C320" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D320" s="11" t="str">
@@ -12196,7 +12203,7 @@
         <v/>
       </c>
       <c r="C321" t="str">
-        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
+        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
         <v/>
       </c>
       <c r="D321" s="11" t="str">
@@ -14117,11 +14124,11 @@
       <c r="A1" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41" t="s">
+      <c r="C1" s="39"/>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
     </row>
@@ -14135,7 +14142,7 @@
       <c r="C2" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="41"/>
+      <c r="D2" s="40"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="e" cm="1" vm="2">
@@ -14758,11 +14765,11 @@
       <c r="A1" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41" t="s">
+      <c r="C1" s="39"/>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
     </row>
@@ -14776,7 +14783,7 @@
       <c r="C2" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="41"/>
+      <c r="D2" s="40"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="e" cm="1" vm="2">

--- a/SOPs/Lab/general-filtering/templates/filtering-lab-data-sheets.xlsx
+++ b/SOPs/Lab/general-filtering/templates/filtering-lab-data-sheets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wampleka\Documents\Projects\WWS-standard-methods\SOPs\Lab\general-filtering\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777A45AA-21E9-49EC-B1CB-AC35032B377D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0DCA28-B70E-4578-844C-E71ABE4372EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FILL ME" sheetId="10" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>Project</t>
   </si>
@@ -250,9 +250,6 @@
   </si>
   <si>
     <t>1. Fill out the information above to auto populate the sample IDs which will autopopulate the datasheets</t>
-  </si>
-  <si>
-    <t>Sample Date/Time</t>
   </si>
   <si>
     <r>
@@ -737,7 +734,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -813,6 +810,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -831,7 +829,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1259,149 +1259,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C19E421-CB14-43E0-8DEF-1EDAC63A74D0}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="35.5703125" customWidth="1"/>
+    <col min="1" max="1" width="39.7265625" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" customWidth="1"/>
+    <col min="4" max="4" width="35.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="36"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B1" s="37"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="D3" s="35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="D3" s="41" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="B4" s="31"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="31" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,D4:D100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="B5" s="31"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="31"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="32"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
+      <c r="B9" s="32"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="37"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="38"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="33"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="33"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>44</v>
-      </c>
       <c r="B12" s="33"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="34"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="14">
-        <f>COUNTA(_xlfn.TEXTSPLIT('FILL ME'!#REF!, ", "))</f>
+        <f>COUNTA(_xlfn.TEXTSPLIT('FILL ME'!B5, ", "))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="29" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
       <c r="D19" s="30"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1416,7 +1411,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B9" xr:uid="{C9223F02-615C-40C0-AC22-D5C65C30523D}">
       <formula1>"Bottle Number, Sample Date/Time"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{697B2588-1EEA-4F76-8C71-F3744F707BF8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{8ECAA109-F226-4344-8B31-1AAA779B2ABB}">
       <formula1>"Grab, ISCO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1428,20 +1423,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94820D06-FFFB-4E0B-84AE-A424BDF68770}">
   <dimension ref="A1:K321"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="9.140625" style="3"/>
+    <col min="1" max="1" width="11.54296875" style="3" customWidth="1"/>
+    <col min="2" max="3" width="9.1796875" style="3"/>
     <col min="4" max="4" width="14" style="3" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="17.26953125" style="3" customWidth="1"/>
     <col min="6" max="6" width="14" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="3"/>
-    <col min="9" max="9" width="16.85546875" style="14" customWidth="1"/>
-    <col min="10" max="10" width="28.7109375" style="14" customWidth="1"/>
-    <col min="11" max="11" width="30.140625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" style="3"/>
+    <col min="9" max="9" width="16.81640625" style="14" customWidth="1"/>
+    <col min="10" max="10" width="28.7265625" style="14" customWidth="1"/>
+    <col min="11" max="11" width="30.1796875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1476,8 +1472,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="str">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1486,7 +1482,7 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D2" s="11" t="str">
@@ -1507,27 +1503,27 @@
       </c>
       <c r="H2" s="3" t="e" cm="1">
         <f t="array" ref="H2">_xlfn.LET(
-    _xlpm.items, _xlfn.TEXTSPLIT('FILL ME'!#REF!, ", "),
+    _xlpm.items, _xlfn.TEXTSPLIT('FILL ME'!B5, ", "),
     _xlpm.x, 'FILL ME'!$B$6,
     INDEX(_xlpm.items, ROUNDUP(_xlfn.SEQUENCE(COUNTA(_xlpm.items)*_xlpm.x)/_xlpm.x, 0))
 )</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="I2" s="14" t="e">
         <f>CONCATENATE(H2,"_",TEXT(G2,"00"))</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J2" s="15" t="e">
         <f>CONCATENATE(C2,"_", H2,"_",D2,"_",TEXT(G2,"00"))</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="K2" s="15" t="e">
         <f>CONCATENATE(C2,"_", H2,"_",TEXT(E2, "yyyymmdd"),"_",TEXT(F2, "hhmm"))</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="str">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1536,7 +1532,7 @@
         <v/>
       </c>
       <c r="C3" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D3" s="11" t="str">
@@ -1564,8 +1560,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="str">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1574,7 +1570,7 @@
         <v/>
       </c>
       <c r="C4" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D4" s="11" t="str">
@@ -1602,8 +1598,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="str">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1612,7 +1608,7 @@
         <v/>
       </c>
       <c r="C5" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D5" s="11" t="str">
@@ -1640,8 +1636,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="str">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1650,7 +1646,7 @@
         <v/>
       </c>
       <c r="C6" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D6" s="11" t="str">
@@ -1678,8 +1674,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="str">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1688,7 +1684,7 @@
         <v/>
       </c>
       <c r="C7" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D7" s="11" t="str">
@@ -1716,8 +1712,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="str">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1726,7 +1722,7 @@
         <v/>
       </c>
       <c r="C8" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D8" s="11" t="str">
@@ -1754,8 +1750,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="str">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1764,7 +1760,7 @@
         <v/>
       </c>
       <c r="C9" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D9" s="11" t="str">
@@ -1792,8 +1788,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="str">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1802,7 +1798,7 @@
         <v/>
       </c>
       <c r="C10" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D10" s="11" t="str">
@@ -1830,8 +1826,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="str">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1840,7 +1836,7 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D11" s="11" t="str">
@@ -1868,8 +1864,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="str">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1878,7 +1874,7 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D12" s="11" t="str">
@@ -1906,8 +1902,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="str">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1916,7 +1912,7 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D13" s="11" t="str">
@@ -1944,8 +1940,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="str">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1954,7 +1950,7 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D14" s="11" t="str">
@@ -1982,8 +1978,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="str">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -1992,7 +1988,7 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D15" s="11" t="str">
@@ -2020,8 +2016,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="str">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2030,7 +2026,7 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D16" s="11" t="str">
@@ -2058,8 +2054,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="str">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2068,7 +2064,7 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D17" s="11" t="str">
@@ -2096,8 +2092,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="str">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2106,7 +2102,7 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D18" s="11" t="str">
@@ -2134,8 +2130,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="str">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2144,7 +2140,7 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D19" s="11" t="str">
@@ -2172,8 +2168,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="str">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2182,7 +2178,7 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D20" s="11" t="str">
@@ -2210,8 +2206,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="str">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2220,7 +2216,7 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D21" s="11" t="str">
@@ -2248,8 +2244,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="str">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2258,7 +2254,7 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D22" s="11" t="str">
@@ -2286,8 +2282,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="str">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2296,7 +2292,7 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D23" s="11" t="str">
@@ -2324,8 +2320,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="str">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2334,7 +2330,7 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D24" s="11" t="str">
@@ -2362,8 +2358,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="str">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2372,7 +2368,7 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D25" s="11" t="str">
@@ -2400,8 +2396,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="str">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2410,7 +2406,7 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D26" s="11" t="str">
@@ -2438,8 +2434,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="str">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2448,7 +2444,7 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D27" s="11" t="str">
@@ -2476,8 +2472,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="str">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2486,7 +2482,7 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D28" s="11" t="str">
@@ -2514,8 +2510,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="str">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2524,7 +2520,7 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D29" s="11" t="str">
@@ -2552,8 +2548,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="str">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2562,7 +2558,7 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D30" s="11" t="str">
@@ -2590,8 +2586,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="str">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2600,7 +2596,7 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D31" s="11" t="str">
@@ -2628,8 +2624,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="str">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2638,7 +2634,7 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D32" s="11" t="str">
@@ -2666,8 +2662,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="str">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2676,7 +2672,7 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D33" s="11" t="str">
@@ -2704,8 +2700,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="str">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A34" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2714,7 +2710,7 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D34" s="11" t="str">
@@ -2742,8 +2738,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="str">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A35" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2752,7 +2748,7 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D35" s="11" t="str">
@@ -2780,8 +2776,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="str">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A36" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2790,7 +2786,7 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D36" s="11" t="str">
@@ -2818,8 +2814,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="str">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2828,7 +2824,7 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D37" s="11" t="str">
@@ -2856,8 +2852,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="str">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A38" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2866,7 +2862,7 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D38" s="11" t="str">
@@ -2894,8 +2890,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="str">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A39" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2904,7 +2900,7 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D39" s="11" t="str">
@@ -2932,8 +2928,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="str">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A40" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2942,7 +2938,7 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D40" s="11" t="str">
@@ -2970,8 +2966,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="str">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A41" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -2980,7 +2976,7 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D41" s="11" t="str">
@@ -3008,8 +3004,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="str">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A42" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3018,7 +3014,7 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D42" s="11" t="str">
@@ -3046,8 +3042,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="str">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A43" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3056,7 +3052,7 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D43" s="11" t="str">
@@ -3084,8 +3080,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="str">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A44" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3094,7 +3090,7 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D44" s="11" t="str">
@@ -3122,8 +3118,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="str">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A45" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3132,7 +3128,7 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D45" s="11" t="str">
@@ -3160,8 +3156,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="str">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A46" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3170,7 +3166,7 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D46" s="11" t="str">
@@ -3198,8 +3194,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="str">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A47" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3208,7 +3204,7 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D47" s="11" t="str">
@@ -3236,8 +3232,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="str">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A48" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3246,7 +3242,7 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D48" s="11" t="str">
@@ -3274,8 +3270,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="str">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A49" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3284,7 +3280,7 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D49" s="11" t="str">
@@ -3312,8 +3308,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="str">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A50" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3322,7 +3318,7 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D50" s="11" t="str">
@@ -3351,8 +3347,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="str">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A51" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3361,7 +3357,7 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D51" s="11" t="str">
@@ -3390,8 +3386,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="str">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A52" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3400,7 +3396,7 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D52" s="11" t="str">
@@ -3429,8 +3425,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="str">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A53" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3439,7 +3435,7 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D53" s="11" t="str">
@@ -3468,8 +3464,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="str">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A54" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3478,7 +3474,7 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D54" s="11" t="str">
@@ -3507,8 +3503,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="str">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A55" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3517,7 +3513,7 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D55" s="11" t="str">
@@ -3546,8 +3542,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="str">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A56" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3556,7 +3552,7 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D56" s="11" t="str">
@@ -3585,8 +3581,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="str">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A57" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3595,7 +3591,7 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D57" s="11" t="str">
@@ -3624,8 +3620,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="str">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A58" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3634,7 +3630,7 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D58" s="11" t="str">
@@ -3663,8 +3659,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="str">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A59" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3673,7 +3669,7 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D59" s="11" t="str">
@@ -3702,8 +3698,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="str">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A60" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3712,7 +3708,7 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D60" s="11" t="str">
@@ -3741,8 +3737,8 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="str">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A61" s="42" t="str">
         <f>'FILL ME'!$B$8</f>
         <v>Grab</v>
       </c>
@@ -3751,7 +3747,7 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D61" s="11" t="str">
@@ -3780,13 +3776,13 @@
         <v>__19000100_</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B62" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C62" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D62" s="11" t="str">
@@ -3815,13 +3811,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B63" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C63" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D63" s="11" t="str">
@@ -3850,13 +3846,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B64" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C64" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D64" s="11" t="str">
@@ -3885,13 +3881,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B65" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C65" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D65" s="11" t="str">
@@ -3920,13 +3916,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B66" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C66" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D66" s="11" t="str">
@@ -3955,13 +3951,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B67" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C67" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D67" s="11" t="str">
@@ -3990,13 +3986,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B68" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C68" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D68" s="11" t="str">
@@ -4025,13 +4021,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B69" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C69" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D69" s="11" t="str">
@@ -4060,13 +4056,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B70" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C70" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D70" s="11" t="str">
@@ -4095,13 +4091,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B71" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C71" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D71" s="11" t="str">
@@ -4130,13 +4126,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B72" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C72" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D72" s="11" t="str">
@@ -4165,13 +4161,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B73" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C73" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D73" s="11" t="str">
@@ -4200,13 +4196,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B74" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C74" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D74" s="11" t="str">
@@ -4235,13 +4231,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B75" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C75" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D75" s="11" t="str">
@@ -4270,13 +4266,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B76" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C76" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D76" s="11" t="str">
@@ -4305,13 +4301,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B77" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C77" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D77" s="11" t="str">
@@ -4340,13 +4336,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B78" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C78" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D78" s="11" t="str">
@@ -4375,13 +4371,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B79" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C79" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D79" s="11" t="str">
@@ -4410,13 +4406,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B80" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C80" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D80" s="11" t="str">
@@ -4445,13 +4441,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B81" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C81" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D81" s="11" t="str">
@@ -4480,13 +4476,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B82" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C82" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D82" s="11" t="str">
@@ -4515,13 +4511,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B83" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C83" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D83" s="11" t="str">
@@ -4550,13 +4546,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B84" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C84" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D84" s="11" t="str">
@@ -4585,13 +4581,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B85" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C85" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D85" s="11" t="str">
@@ -4620,13 +4616,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B86" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C86" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D86" s="11" t="str">
@@ -4655,13 +4651,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B87" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C87" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D87" s="11" t="str">
@@ -4690,13 +4686,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B88" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C88" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D88" s="11" t="str">
@@ -4725,13 +4721,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B89" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C89" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D89" s="11" t="str">
@@ -4760,13 +4756,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B90" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C90" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D90" s="11" t="str">
@@ -4795,13 +4791,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B91" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C91" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D91" s="11" t="str">
@@ -4830,13 +4826,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B92" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C92" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D92" s="11" t="str">
@@ -4865,13 +4861,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B93" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C93" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D93" s="11" t="str">
@@ -4900,13 +4896,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B94" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C94" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D94" s="11" t="str">
@@ -4935,13 +4931,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B95" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C95" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D95" s="11" t="str">
@@ -4970,13 +4966,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B96" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C96" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D96" s="11" t="str">
@@ -5005,13 +5001,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B97" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C97" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D97" s="11" t="str">
@@ -5040,13 +5036,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B98" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C98" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D98" s="11" t="str">
@@ -5075,13 +5071,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B99" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C99" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D99" s="11" t="str">
@@ -5110,13 +5106,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B100" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C100" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D100" s="11" t="str">
@@ -5145,13 +5141,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B101" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C101" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D101" s="11" t="str">
@@ -5180,13 +5176,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B102" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C102" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D102" s="11" t="str">
@@ -5215,13 +5211,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B103" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C103" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D103" s="11" t="str">
@@ -5250,13 +5246,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B104" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C104" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D104" s="11" t="str">
@@ -5285,13 +5281,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B105" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C105" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D105" s="11" t="str">
@@ -5317,13 +5313,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B106" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C106" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D106" s="11" t="str">
@@ -5349,13 +5345,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B107" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C107" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D107" s="11" t="str">
@@ -5381,13 +5377,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B108" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C108" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D108" s="11" t="str">
@@ -5413,13 +5409,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B109" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C109" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D109" s="11" t="str">
@@ -5445,13 +5441,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B110" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C110" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D110" s="11" t="str">
@@ -5477,13 +5473,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B111" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C111" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D111" s="11" t="str">
@@ -5509,13 +5505,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B112" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C112" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D112" s="11" t="str">
@@ -5541,13 +5537,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B113" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C113" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D113" s="11" t="str">
@@ -5573,13 +5569,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B114" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C114" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D114" s="11" t="str">
@@ -5605,13 +5601,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B115" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C115" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D115" s="11" t="str">
@@ -5637,13 +5633,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B116" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C116" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D116" s="11" t="str">
@@ -5669,13 +5665,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B117" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C117" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D117" s="11" t="str">
@@ -5701,13 +5697,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B118" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C118" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D118" s="11" t="str">
@@ -5733,13 +5729,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B119" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C119" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D119" s="11" t="str">
@@ -5765,13 +5761,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B120" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C120" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D120" s="11" t="str">
@@ -5797,13 +5793,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B121" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C121" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D121" s="11" t="str">
@@ -5829,13 +5825,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B122" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C122" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D122" s="11" t="str">
@@ -5861,13 +5857,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B123" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C123" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D123" s="11" t="str">
@@ -5893,13 +5889,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B124" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C124" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D124" s="11" t="str">
@@ -5925,13 +5921,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B125" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C125" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D125" s="11" t="str">
@@ -5957,13 +5953,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B126" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C126" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D126" s="11" t="str">
@@ -5989,13 +5985,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B127" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C127" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D127" s="11" t="str">
@@ -6021,13 +6017,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B128" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C128" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D128" s="11" t="str">
@@ -6053,13 +6049,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B129" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C129" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D129" s="11" t="str">
@@ -6085,13 +6081,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B130" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C130" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D130" s="11" t="str">
@@ -6117,13 +6113,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B131" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C131" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D131" s="11" t="str">
@@ -6149,13 +6145,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B132" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C132" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D132" s="11" t="str">
@@ -6181,13 +6177,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B133" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C133" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D133" s="11" t="str">
@@ -6213,13 +6209,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B134" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C134" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D134" s="11" t="str">
@@ -6245,13 +6241,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B135" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C135" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D135" s="11" t="str">
@@ -6277,13 +6273,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B136" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C136" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D136" s="11" t="str">
@@ -6309,13 +6305,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B137" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C137" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D137" s="11" t="str">
@@ -6341,13 +6337,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B138" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C138" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D138" s="11" t="str">
@@ -6373,13 +6369,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B139" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C139" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D139" s="11" t="str">
@@ -6405,13 +6401,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B140" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C140" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D140" s="11" t="str">
@@ -6437,13 +6433,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B141" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C141" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D141" s="11" t="str">
@@ -6469,13 +6465,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B142" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C142" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D142" s="11" t="str">
@@ -6501,13 +6497,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B143" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C143" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D143" s="11" t="str">
@@ -6533,13 +6529,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B144" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C144" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D144" s="11" t="str">
@@ -6565,13 +6561,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B145" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C145" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D145" s="11" t="str">
@@ -6597,13 +6593,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B146" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C146" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D146" s="11" t="str">
@@ -6629,13 +6625,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B147" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C147" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D147" s="11" t="str">
@@ -6661,13 +6657,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B148" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C148" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D148" s="11" t="str">
@@ -6693,13 +6689,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B149" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C149" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D149" s="11" t="str">
@@ -6725,13 +6721,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B150" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C150" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D150" s="11" t="str">
@@ -6757,13 +6753,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B151" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C151" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D151" s="11" t="str">
@@ -6789,13 +6785,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B152" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C152" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D152" s="11" t="str">
@@ -6821,13 +6817,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B153" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C153" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D153" s="11" t="str">
@@ -6853,13 +6849,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B154" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C154" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D154" s="11" t="str">
@@ -6885,13 +6881,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B155" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C155" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D155" s="11" t="str">
@@ -6917,13 +6913,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B156" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C156" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D156" s="11" t="str">
@@ -6949,13 +6945,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B157" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C157" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D157" s="11" t="str">
@@ -6981,13 +6977,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B158" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C158" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D158" s="11" t="str">
@@ -7013,13 +7009,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B159" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C159" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D159" s="11" t="str">
@@ -7045,13 +7041,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B160" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C160" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D160" s="11" t="str">
@@ -7077,13 +7073,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B161" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C161" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D161" s="11" t="str">
@@ -7109,13 +7105,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B162" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C162" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D162" s="11" t="str">
@@ -7141,13 +7137,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B163" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C163" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D163" s="11" t="str">
@@ -7173,13 +7169,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B164" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C164" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D164" s="11" t="str">
@@ -7205,13 +7201,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B165" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C165" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D165" s="11" t="str">
@@ -7237,13 +7233,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B166" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C166" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D166" s="11" t="str">
@@ -7269,13 +7265,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B167" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C167" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D167" s="11" t="str">
@@ -7301,13 +7297,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B168" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C168" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D168" s="11" t="str">
@@ -7333,13 +7329,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B169" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C169" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D169" s="11" t="str">
@@ -7365,13 +7361,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B170" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C170" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D170" s="11" t="str">
@@ -7397,13 +7393,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B171" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C171" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D171" s="11" t="str">
@@ -7429,13 +7425,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B172" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C172" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D172" s="11" t="str">
@@ -7461,13 +7457,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B173" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C173" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D173" s="11" t="str">
@@ -7493,13 +7489,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B174" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C174" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D174" s="11" t="str">
@@ -7525,13 +7521,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="175" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B175" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C175" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D175" s="11" t="str">
@@ -7557,13 +7553,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B176" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C176" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D176" s="11" t="str">
@@ -7589,13 +7585,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B177" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C177" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D177" s="11" t="str">
@@ -7621,13 +7617,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B178" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C178" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D178" s="11" t="str">
@@ -7653,13 +7649,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B179" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C179" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D179" s="11" t="str">
@@ -7685,13 +7681,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B180" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C180" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D180" s="11" t="str">
@@ -7717,13 +7713,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B181" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C181" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D181" s="11" t="str">
@@ -7749,13 +7745,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B182" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C182" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D182" s="11" t="str">
@@ -7781,13 +7777,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B183" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C183" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D183" s="11" t="str">
@@ -7813,13 +7809,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B184" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C184" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D184" s="11" t="str">
@@ -7845,13 +7841,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B185" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C185" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D185" s="11" t="str">
@@ -7877,13 +7873,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B186" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C186" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D186" s="11" t="str">
@@ -7909,13 +7905,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B187" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C187" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D187" s="11" t="str">
@@ -7941,13 +7937,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B188" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C188" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D188" s="11" t="str">
@@ -7973,13 +7969,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B189" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C189" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D189" s="11" t="str">
@@ -8005,13 +8001,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B190" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C190" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D190" s="11" t="str">
@@ -8037,13 +8033,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B191" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C191" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D191" s="11" t="str">
@@ -8069,13 +8065,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B192" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C192" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D192" s="11" t="str">
@@ -8101,13 +8097,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="193" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B193" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C193" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D193" s="11" t="str">
@@ -8133,13 +8129,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="194" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B194" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C194" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D194" s="11" t="str">
@@ -8165,13 +8161,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="195" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B195" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C195" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D195" s="11" t="str">
@@ -8197,13 +8193,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="196" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B196" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C196" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D196" s="11" t="str">
@@ -8229,13 +8225,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="197" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B197" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C197" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D197" s="11" t="str">
@@ -8261,13 +8257,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="198" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B198" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C198" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D198" s="11" t="str">
@@ -8293,13 +8289,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="199" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B199" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C199" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D199" s="11" t="str">
@@ -8325,13 +8321,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="200" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B200" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C200" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D200" s="11" t="str">
@@ -8357,13 +8353,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="201" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B201" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C201" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D201" s="11" t="str">
@@ -8389,13 +8385,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="202" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B202" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C202" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D202" s="11" t="str">
@@ -8421,13 +8417,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="203" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B203" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C203" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D203" s="11" t="str">
@@ -8453,13 +8449,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="204" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B204" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C204" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D204" s="11" t="str">
@@ -8485,13 +8481,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="205" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B205" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C205" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D205" s="11" t="str">
@@ -8517,13 +8513,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="206" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B206" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C206" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D206" s="11" t="str">
@@ -8549,13 +8545,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B207" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C207" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D207" s="11" t="str">
@@ -8581,13 +8577,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="208" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B208" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C208" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D208" s="11" t="str">
@@ -8613,13 +8609,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="209" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B209" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C209" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D209" s="11" t="str">
@@ -8645,13 +8641,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="210" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B210" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C210" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D210" s="11" t="str">
@@ -8677,13 +8673,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="211" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B211" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C211" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D211" s="11" t="str">
@@ -8709,13 +8705,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="212" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B212" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C212" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D212" s="11" t="str">
@@ -8741,13 +8737,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="213" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B213" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C213" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D213" s="11" t="str">
@@ -8773,13 +8769,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="214" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B214" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C214" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D214" s="11" t="str">
@@ -8805,13 +8801,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="215" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B215" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C215" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D215" s="11" t="str">
@@ -8837,13 +8833,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="216" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B216" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C216" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D216" s="11" t="str">
@@ -8869,13 +8865,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="217" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B217" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C217" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D217" s="11" t="str">
@@ -8901,13 +8897,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="218" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B218" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C218" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D218" s="11" t="str">
@@ -8933,13 +8929,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="219" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B219" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C219" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D219" s="11" t="str">
@@ -8965,13 +8961,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="220" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B220" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C220" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D220" s="11" t="str">
@@ -8997,13 +8993,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="221" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B221" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C221" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D221" s="11" t="str">
@@ -9029,13 +9025,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="222" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B222" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C222" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D222" s="11" t="str">
@@ -9061,13 +9057,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="223" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B223" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C223" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D223" s="11" t="str">
@@ -9093,13 +9089,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="224" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B224" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C224" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D224" s="11" t="str">
@@ -9125,13 +9121,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="225" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B225" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C225" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D225" s="11" t="str">
@@ -9157,13 +9153,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="226" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B226" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C226" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D226" s="11" t="str">
@@ -9189,13 +9185,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="227" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B227" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C227" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D227" s="11" t="str">
@@ -9221,13 +9217,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="228" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B228" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C228" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D228" s="11" t="str">
@@ -9253,13 +9249,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="229" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B229" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C229" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D229" s="11" t="str">
@@ -9285,13 +9281,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="230" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B230" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C230" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D230" s="11" t="str">
@@ -9317,13 +9313,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="231" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B231" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C231" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D231" s="11" t="str">
@@ -9349,13 +9345,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="232" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B232" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C232" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D232" s="11" t="str">
@@ -9381,13 +9377,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="233" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B233" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C233" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D233" s="11" t="str">
@@ -9413,13 +9409,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="234" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B234" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C234" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D234" s="11" t="str">
@@ -9445,13 +9441,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="235" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B235" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C235" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D235" s="11" t="str">
@@ -9477,13 +9473,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="236" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B236" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C236" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D236" s="11" t="str">
@@ -9509,13 +9505,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="237" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B237" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C237" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D237" s="11" t="str">
@@ -9541,13 +9537,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="238" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B238" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C238" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D238" s="11" t="str">
@@ -9573,13 +9569,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B239" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C239" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D239" s="11" t="str">
@@ -9605,13 +9601,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="240" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B240" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C240" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D240" s="11" t="str">
@@ -9637,13 +9633,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="241" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B241" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C241" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D241" s="11" t="str">
@@ -9669,13 +9665,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="242" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B242" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C242" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D242" s="11" t="str">
@@ -9701,13 +9697,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="243" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B243" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C243" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D243" s="11" t="str">
@@ -9733,13 +9729,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="244" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B244" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C244" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D244" s="11" t="str">
@@ -9765,13 +9761,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="245" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B245" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C245" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D245" s="11" t="str">
@@ -9797,13 +9793,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="246" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B246" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C246" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D246" s="11" t="str">
@@ -9829,13 +9825,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="247" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B247" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C247" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D247" s="11" t="str">
@@ -9861,13 +9857,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="248" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B248" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C248" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D248" s="11" t="str">
@@ -9893,13 +9889,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="249" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B249" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C249" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D249" s="11" t="str">
@@ -9925,13 +9921,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="250" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B250" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C250" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D250" s="11" t="str">
@@ -9957,13 +9953,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="251" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B251" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C251" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D251" s="11" t="str">
@@ -9989,13 +9985,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="252" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B252" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C252" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D252" s="11" t="str">
@@ -10021,13 +10017,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="253" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B253" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C253" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D253" s="11" t="str">
@@ -10053,13 +10049,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="254" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B254" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C254" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D254" s="11" t="str">
@@ -10085,13 +10081,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="255" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B255" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C255" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D255" s="11" t="str">
@@ -10117,13 +10113,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="256" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B256" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C256" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D256" s="11" t="str">
@@ -10149,13 +10145,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="257" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B257" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C257" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D257" s="11" t="str">
@@ -10181,13 +10177,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="258" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B258" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C258" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D258" s="11" t="str">
@@ -10213,13 +10209,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="259" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B259" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C259" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D259" s="11" t="str">
@@ -10245,13 +10241,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="260" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B260" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C260" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D260" s="11" t="str">
@@ -10277,13 +10273,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="261" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B261" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C261" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D261" s="11" t="str">
@@ -10309,13 +10305,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="262" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B262" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C262" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D262" s="11" t="str">
@@ -10341,13 +10337,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="263" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B263" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C263" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D263" s="11" t="str">
@@ -10373,13 +10369,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="264" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B264" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C264" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D264" s="11" t="str">
@@ -10405,13 +10401,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="265" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B265" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C265" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D265" s="11" t="str">
@@ -10437,13 +10433,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="266" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B266" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C266" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D266" s="11" t="str">
@@ -10469,13 +10465,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="267" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B267" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C267" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D267" s="11" t="str">
@@ -10501,13 +10497,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="268" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B268" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C268" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D268" s="11" t="str">
@@ -10533,13 +10529,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="269" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B269" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C269" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D269" s="11" t="str">
@@ -10565,13 +10561,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="270" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B270" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C270" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D270" s="11" t="str">
@@ -10597,13 +10593,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="271" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B271" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C271" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D271" s="11" t="str">
@@ -10629,13 +10625,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="272" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B272" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C272" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D272" s="11" t="str">
@@ -10661,13 +10657,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="273" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B273" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C273" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D273" s="11" t="str">
@@ -10693,13 +10689,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="274" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B274" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C274" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D274" s="11" t="str">
@@ -10725,13 +10721,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="275" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B275" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C275" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D275" s="11" t="str">
@@ -10757,13 +10753,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="276" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B276" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C276" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D276" s="11" t="str">
@@ -10789,13 +10785,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="277" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B277" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C277" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D277" s="11" t="str">
@@ -10821,13 +10817,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="278" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B278" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C278" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D278" s="11" t="str">
@@ -10853,13 +10849,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="279" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B279" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C279" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D279" s="11" t="str">
@@ -10885,13 +10881,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="280" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B280" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C280" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D280" s="11" t="str">
@@ -10917,13 +10913,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="281" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B281" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C281" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D281" s="11" t="str">
@@ -10949,13 +10945,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="282" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B282" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C282" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D282" s="11" t="str">
@@ -10981,13 +10977,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="283" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B283" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C283" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D283" s="11" t="str">
@@ -11013,13 +11009,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="284" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B284" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C284" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D284" s="11" t="str">
@@ -11045,13 +11041,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="285" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B285" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C285" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D285" s="11" t="str">
@@ -11077,13 +11073,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="286" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B286" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C286" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D286" s="11" t="str">
@@ -11109,13 +11105,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="287" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B287" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C287" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D287" s="11" t="str">
@@ -11141,13 +11137,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="288" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B288" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C288" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D288" s="11" t="str">
@@ -11173,13 +11169,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="289" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B289" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C289" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D289" s="11" t="str">
@@ -11205,13 +11201,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="290" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B290" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C290" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D290" s="11" t="str">
@@ -11237,13 +11233,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="291" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B291" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C291" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D291" s="11" t="str">
@@ -11269,13 +11265,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="292" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B292" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C292" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D292" s="11" t="str">
@@ -11301,13 +11297,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="293" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B293" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C293" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D293" s="11" t="str">
@@ -11333,13 +11329,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="294" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B294" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C294" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D294" s="11" t="str">
@@ -11365,13 +11361,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="295" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B295" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C295" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D295" s="11" t="str">
@@ -11397,13 +11393,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="296" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B296" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C296" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D296" s="11" t="str">
@@ -11429,13 +11425,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="297" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B297" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C297" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D297" s="11" t="str">
@@ -11461,13 +11457,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="298" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B298" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C298" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D298" s="11" t="str">
@@ -11493,13 +11489,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="299" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B299" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C299" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D299" s="11" t="str">
@@ -11525,13 +11521,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="300" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B300" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C300" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D300" s="11" t="str">
@@ -11557,13 +11553,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="301" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B301" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C301" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D301" s="11" t="str">
@@ -11589,13 +11585,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="302" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B302" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C302" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D302" s="11" t="str">
@@ -11621,13 +11617,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="303" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B303" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C303" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D303" s="11" t="str">
@@ -11653,13 +11649,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="304" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B304" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C304" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D304" s="11" t="str">
@@ -11685,13 +11681,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="305" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B305" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C305" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D305" s="11" t="str">
@@ -11717,13 +11713,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="306" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B306" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C306" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D306" s="11" t="str">
@@ -11749,13 +11745,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="307" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B307" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C307" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D307" s="11" t="str">
@@ -11781,13 +11777,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="308" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B308" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C308" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D308" s="11" t="str">
@@ -11813,13 +11809,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="309" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B309" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C309" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D309" s="11" t="str">
@@ -11845,13 +11841,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="310" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B310" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C310" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D310" s="11" t="str">
@@ -11877,13 +11873,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="311" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B311" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C311" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D311" s="11" t="str">
@@ -11909,13 +11905,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="312" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B312" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C312" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D312" s="11" t="str">
@@ -11941,13 +11937,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="313" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B313" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C313" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D313" s="11" t="str">
@@ -11973,13 +11969,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="314" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B314" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C314" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D314" s="11" t="str">
@@ -12005,13 +12001,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="315" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B315" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C315" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D315" s="11" t="str">
@@ -12037,13 +12033,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="316" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B316" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C316" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D316" s="11" t="str">
@@ -12069,13 +12065,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="317" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B317" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C317" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D317" s="11" t="str">
@@ -12101,13 +12097,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="318" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B318" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C318" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D318" s="11" t="str">
@@ -12133,13 +12129,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="319" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B319" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C319" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D319" s="11" t="str">
@@ -12165,13 +12161,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="320" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B320" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C320" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D320" s="11" t="str">
@@ -12197,13 +12193,13 @@
         <v>__19000100_0000</v>
       </c>
     </row>
-    <row r="321" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B321" t="str">
         <f>IF('FILL ME'!$B$3 = "", "", 'FILL ME'!$B$3)</f>
         <v/>
       </c>
       <c r="C321" t="str">
-        <f>IF('FILL ME'!$B$5 = "", "", 'FILL ME'!$B$5)</f>
+        <f>IF('FILL ME'!$B$4 = "", "", 'FILL ME'!$B$4)</f>
         <v/>
       </c>
       <c r="D321" s="11" t="str">
@@ -12270,17 +12266,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F438"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="41.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" customWidth="1"/>
+    <col min="3" max="3" width="18.7265625" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="6" max="6" width="41.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
         <v>22</v>
       </c>
@@ -12300,7 +12296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>17</v>
       </c>
@@ -12320,7 +12316,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="e" cm="1" vm="2">
         <f t="array" ref="A3">_xlfn.CHOOSEROWS(
     IF('FILL ME'!B9="Bottle Number", 'Label IDs'!J:J, 'Label IDs'!K:K),
@@ -12334,7 +12330,7 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -12342,7 +12338,7 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="21"/>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
@@ -12350,7 +12346,7 @@
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -12358,7 +12354,7 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="21"/>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
@@ -12366,7 +12362,7 @@
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -12374,7 +12370,7 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
@@ -12382,7 +12378,7 @@
       <c r="E9" s="21"/>
       <c r="F9" s="21"/>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -12390,7 +12386,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="21"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -12398,7 +12394,7 @@
       <c r="E11" s="21"/>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -12406,7 +12402,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -12414,7 +12410,7 @@
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -12422,7 +12418,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -12430,7 +12426,7 @@
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
     </row>
-    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -12438,7 +12434,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -12446,7 +12442,7 @@
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -12454,7 +12450,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -12462,7 +12458,7 @@
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -12470,7 +12466,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="21"/>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -12478,7 +12474,7 @@
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -12486,7 +12482,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
@@ -12494,7 +12490,7 @@
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -12502,7 +12498,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="21"/>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -12510,7 +12506,7 @@
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -12518,7 +12514,7 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="21"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -12526,7 +12522,7 @@
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -12534,7 +12530,7 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="21"/>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -12542,7 +12538,7 @@
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -12550,7 +12546,7 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="21"/>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
@@ -12558,7 +12554,7 @@
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -12566,7 +12562,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="21"/>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -12574,7 +12570,7 @@
       <c r="E33" s="21"/>
       <c r="F33" s="21"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -12582,7 +12578,7 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
@@ -12590,7 +12586,7 @@
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -12598,7 +12594,7 @@
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="21"/>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -12606,7 +12602,7 @@
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -12614,7 +12610,7 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="21"/>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -12622,7 +12618,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="21"/>
     </row>
-    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -12630,7 +12626,7 @@
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="21"/>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
@@ -12638,7 +12634,7 @@
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
     </row>
-    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -12646,7 +12642,7 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="21"/>
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
@@ -12654,7 +12650,7 @@
       <c r="E43" s="21"/>
       <c r="F43" s="21"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="9"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -12662,7 +12658,7 @@
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="21"/>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
@@ -12670,7 +12666,7 @@
       <c r="E45" s="20"/>
       <c r="F45" s="20"/>
     </row>
-    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="9"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -12678,7 +12674,7 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="21"/>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
@@ -12686,7 +12682,7 @@
       <c r="E47" s="20"/>
       <c r="F47" s="20"/>
     </row>
-    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="9"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -12694,7 +12690,7 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
     </row>
-    <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="21"/>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
@@ -12702,7 +12698,7 @@
       <c r="E49" s="20"/>
       <c r="F49" s="20"/>
     </row>
-    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="9"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -12710,7 +12706,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
     </row>
-    <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="21"/>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
@@ -12718,7 +12714,7 @@
       <c r="E51" s="20"/>
       <c r="F51" s="20"/>
     </row>
-    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="9"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -12726,7 +12722,7 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
     </row>
-    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="21"/>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
@@ -12734,7 +12730,7 @@
       <c r="E53" s="20"/>
       <c r="F53" s="20"/>
     </row>
-    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="9"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -12742,7 +12738,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="21"/>
       <c r="B55" s="20"/>
       <c r="C55" s="20"/>
@@ -12750,7 +12746,7 @@
       <c r="E55" s="20"/>
       <c r="F55" s="20"/>
     </row>
-    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="9"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -12758,7 +12754,7 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="21"/>
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
@@ -12766,7 +12762,7 @@
       <c r="E57" s="20"/>
       <c r="F57" s="20"/>
     </row>
-    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="9"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -12774,7 +12770,7 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
     </row>
-    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="21"/>
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
@@ -12782,7 +12778,7 @@
       <c r="E59" s="20"/>
       <c r="F59" s="20"/>
     </row>
-    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="9"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -12790,7 +12786,7 @@
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
     </row>
-    <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="21"/>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -12798,7 +12794,7 @@
       <c r="E61" s="20"/>
       <c r="F61" s="20"/>
     </row>
-    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="9"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -12806,7 +12802,7 @@
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
     </row>
-    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="21"/>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -12814,7 +12810,7 @@
       <c r="E63" s="20"/>
       <c r="F63" s="20"/>
     </row>
-    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="9"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -12822,7 +12818,7 @@
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
     </row>
-    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="21"/>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -12830,7 +12826,7 @@
       <c r="E65" s="20"/>
       <c r="F65" s="20"/>
     </row>
-    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="9"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -12838,7 +12834,7 @@
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
     </row>
-    <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="21"/>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -12846,7 +12842,7 @@
       <c r="E67" s="20"/>
       <c r="F67" s="20"/>
     </row>
-    <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="9"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -12854,7 +12850,7 @@
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
     </row>
-    <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="21"/>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -12862,7 +12858,7 @@
       <c r="E69" s="20"/>
       <c r="F69" s="20"/>
     </row>
-    <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="9"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -12870,7 +12866,7 @@
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
     </row>
-    <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="21"/>
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
@@ -12878,7 +12874,7 @@
       <c r="E71" s="20"/>
       <c r="F71" s="20"/>
     </row>
-    <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="9"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -12886,7 +12882,7 @@
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
     </row>
-    <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="21"/>
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
@@ -12894,7 +12890,7 @@
       <c r="E73" s="20"/>
       <c r="F73" s="20"/>
     </row>
-    <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="9"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -12902,7 +12898,7 @@
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
     </row>
-    <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="21"/>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -12910,7 +12906,7 @@
       <c r="E75" s="20"/>
       <c r="F75" s="20"/>
     </row>
-    <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="9"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -12918,7 +12914,7 @@
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
     </row>
-    <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="21"/>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
@@ -12926,7 +12922,7 @@
       <c r="E77" s="20"/>
       <c r="F77" s="20"/>
     </row>
-    <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="9"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -12934,7 +12930,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
     </row>
-    <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="21"/>
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
@@ -12942,7 +12938,7 @@
       <c r="E79" s="20"/>
       <c r="F79" s="20"/>
     </row>
-    <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="9"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -12950,7 +12946,7 @@
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
     </row>
-    <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="21"/>
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
@@ -12958,7 +12954,7 @@
       <c r="E81" s="20"/>
       <c r="F81" s="20"/>
     </row>
-    <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="9"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -12966,7 +12962,7 @@
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
     </row>
-    <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="21"/>
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
@@ -12974,7 +12970,7 @@
       <c r="E83" s="20"/>
       <c r="F83" s="20"/>
     </row>
-    <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="9"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -12982,7 +12978,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
     </row>
-    <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="21"/>
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
@@ -12990,7 +12986,7 @@
       <c r="E85" s="20"/>
       <c r="F85" s="20"/>
     </row>
-    <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="9"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -12998,7 +12994,7 @@
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
     </row>
-    <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="21"/>
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
@@ -13006,7 +13002,7 @@
       <c r="E87" s="20"/>
       <c r="F87" s="20"/>
     </row>
-    <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="9"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -13014,7 +13010,7 @@
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
     </row>
-    <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="21"/>
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
@@ -13022,7 +13018,7 @@
       <c r="E89" s="20"/>
       <c r="F89" s="20"/>
     </row>
-    <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="9"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -13030,7 +13026,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
     </row>
-    <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="21"/>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
@@ -13038,7 +13034,7 @@
       <c r="E91" s="20"/>
       <c r="F91" s="20"/>
     </row>
-    <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="9"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
@@ -13046,7 +13042,7 @@
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
     </row>
-    <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="21"/>
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
@@ -13054,7 +13050,7 @@
       <c r="E93" s="20"/>
       <c r="F93" s="20"/>
     </row>
-    <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="9"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -13062,1036 +13058,1036 @@
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
     </row>
-    <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="2"/>
     </row>
-    <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="2"/>
     </row>
-    <row r="97" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="2"/>
     </row>
-    <row r="98" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="2"/>
     </row>
-    <row r="99" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="2"/>
     </row>
-    <row r="100" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="2"/>
     </row>
-    <row r="101" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="2"/>
     </row>
-    <row r="102" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="2"/>
     </row>
-    <row r="103" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="2"/>
     </row>
-    <row r="104" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="2"/>
     </row>
-    <row r="105" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="2"/>
     </row>
-    <row r="106" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="2"/>
     </row>
-    <row r="107" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="2"/>
     </row>
-    <row r="108" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="2"/>
     </row>
-    <row r="109" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="2"/>
     </row>
-    <row r="110" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="2"/>
     </row>
-    <row r="111" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="2"/>
     </row>
-    <row r="112" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="2"/>
     </row>
-    <row r="113" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="2"/>
     </row>
-    <row r="114" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="2"/>
     </row>
-    <row r="115" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="2"/>
     </row>
-    <row r="116" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="2"/>
     </row>
-    <row r="117" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="2"/>
     </row>
-    <row r="118" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="2"/>
     </row>
-    <row r="119" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="2"/>
     </row>
-    <row r="120" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="2"/>
     </row>
-    <row r="121" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="2"/>
     </row>
-    <row r="122" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="2"/>
     </row>
-    <row r="123" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="2"/>
     </row>
-    <row r="124" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="2"/>
     </row>
-    <row r="125" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="2"/>
     </row>
-    <row r="126" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="2"/>
     </row>
-    <row r="127" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="2"/>
     </row>
-    <row r="128" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="2"/>
     </row>
-    <row r="129" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="2"/>
     </row>
-    <row r="130" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="2"/>
     </row>
-    <row r="131" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="2"/>
     </row>
-    <row r="132" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="2"/>
     </row>
-    <row r="133" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="2"/>
     </row>
-    <row r="134" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="2"/>
     </row>
-    <row r="135" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="2"/>
     </row>
-    <row r="136" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="2"/>
     </row>
-    <row r="137" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="2"/>
     </row>
-    <row r="138" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="2"/>
     </row>
-    <row r="139" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="2"/>
     </row>
-    <row r="140" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="2"/>
     </row>
-    <row r="141" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="2"/>
     </row>
-    <row r="142" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="2"/>
     </row>
-    <row r="143" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="2"/>
     </row>
-    <row r="144" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="2"/>
     </row>
-    <row r="145" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="2"/>
     </row>
-    <row r="146" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="2"/>
     </row>
-    <row r="147" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="2"/>
     </row>
-    <row r="148" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="2"/>
     </row>
-    <row r="149" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="2"/>
     </row>
-    <row r="150" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" s="2"/>
     </row>
-    <row r="151" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" s="2"/>
     </row>
-    <row r="152" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" s="2"/>
     </row>
-    <row r="153" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="2"/>
     </row>
-    <row r="154" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" s="2"/>
     </row>
-    <row r="155" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" s="2"/>
     </row>
-    <row r="156" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" s="2"/>
     </row>
-    <row r="157" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" s="2"/>
     </row>
-    <row r="158" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" s="2"/>
     </row>
-    <row r="159" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" s="2"/>
     </row>
-    <row r="160" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" s="2"/>
     </row>
-    <row r="161" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" s="2"/>
     </row>
-    <row r="162" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" s="2"/>
     </row>
-    <row r="163" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" s="2"/>
     </row>
-    <row r="164" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" s="2"/>
     </row>
-    <row r="165" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" s="2"/>
     </row>
-    <row r="166" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" s="2"/>
     </row>
-    <row r="167" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" s="2"/>
     </row>
-    <row r="168" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" s="2"/>
     </row>
-    <row r="169" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" s="2"/>
     </row>
-    <row r="170" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" s="2"/>
     </row>
-    <row r="171" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" s="2"/>
     </row>
-    <row r="172" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="2"/>
     </row>
-    <row r="173" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" s="2"/>
     </row>
-    <row r="174" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" s="2"/>
     </row>
-    <row r="175" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" s="2"/>
     </row>
-    <row r="176" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" s="2"/>
     </row>
-    <row r="177" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" s="2"/>
     </row>
-    <row r="178" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
     </row>
-    <row r="179" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="2"/>
     </row>
-    <row r="180" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" s="2"/>
     </row>
-    <row r="181" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" s="2"/>
     </row>
-    <row r="182" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" s="2"/>
     </row>
-    <row r="183" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" s="2"/>
     </row>
-    <row r="184" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" s="2"/>
     </row>
-    <row r="185" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" s="2"/>
     </row>
-    <row r="186" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" s="2"/>
     </row>
-    <row r="187" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" s="2"/>
     </row>
-    <row r="188" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="2"/>
     </row>
-    <row r="189" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" s="2"/>
     </row>
-    <row r="190" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" s="2"/>
     </row>
-    <row r="191" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="2"/>
     </row>
-    <row r="192" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" s="2"/>
     </row>
-    <row r="193" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A193" s="2"/>
     </row>
-    <row r="194" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A194" s="2"/>
     </row>
-    <row r="195" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A195" s="2"/>
     </row>
-    <row r="196" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A196" s="2"/>
     </row>
-    <row r="197" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A197" s="2"/>
     </row>
-    <row r="198" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" s="2"/>
     </row>
-    <row r="199" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" s="2"/>
     </row>
-    <row r="200" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A200" s="2"/>
     </row>
-    <row r="201" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A201" s="2"/>
     </row>
-    <row r="202" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A202" s="2"/>
     </row>
-    <row r="203" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A203" s="2"/>
     </row>
-    <row r="204" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A204" s="2"/>
     </row>
-    <row r="205" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A205" s="2"/>
     </row>
-    <row r="206" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A206" s="2"/>
     </row>
-    <row r="207" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" s="2"/>
     </row>
-    <row r="208" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" s="2"/>
     </row>
-    <row r="209" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A209" s="2"/>
     </row>
-    <row r="210" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A210" s="2"/>
     </row>
-    <row r="211" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A211" s="2"/>
     </row>
-    <row r="212" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A212" s="2"/>
     </row>
-    <row r="213" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A213" s="2"/>
     </row>
-    <row r="214" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A214" s="2"/>
     </row>
-    <row r="215" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A215" s="2"/>
     </row>
-    <row r="216" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A216" s="2"/>
     </row>
-    <row r="217" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A217" s="2"/>
     </row>
-    <row r="218" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A218" s="2"/>
     </row>
-    <row r="219" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A219" s="2"/>
     </row>
-    <row r="220" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A220" s="2"/>
     </row>
-    <row r="221" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A221" s="2"/>
     </row>
-    <row r="222" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A222" s="2"/>
     </row>
-    <row r="223" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A223" s="2"/>
     </row>
-    <row r="224" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A224" s="2"/>
     </row>
-    <row r="225" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A225" s="2"/>
     </row>
-    <row r="226" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A226" s="2"/>
     </row>
-    <row r="227" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A227" s="2"/>
     </row>
-    <row r="228" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A228" s="2"/>
     </row>
-    <row r="229" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A229" s="2"/>
     </row>
-    <row r="230" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A230" s="2"/>
     </row>
-    <row r="231" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A231" s="2"/>
     </row>
-    <row r="232" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" s="2"/>
     </row>
-    <row r="233" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A233" s="2"/>
     </row>
-    <row r="234" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A234" s="2"/>
     </row>
-    <row r="235" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A235" s="2"/>
     </row>
-    <row r="236" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A236" s="2"/>
     </row>
-    <row r="237" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A237" s="2"/>
     </row>
-    <row r="238" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A238" s="2"/>
     </row>
-    <row r="239" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A239" s="2"/>
     </row>
-    <row r="240" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A240" s="2"/>
     </row>
-    <row r="241" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A241" s="2"/>
     </row>
-    <row r="242" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A242" s="2"/>
     </row>
-    <row r="243" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A243" s="2"/>
     </row>
-    <row r="244" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A244" s="2"/>
     </row>
-    <row r="245" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A245" s="2"/>
     </row>
-    <row r="246" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A246" s="2"/>
     </row>
-    <row r="247" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A247" s="2"/>
     </row>
-    <row r="248" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A248" s="2"/>
     </row>
-    <row r="249" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A249" s="2"/>
     </row>
-    <row r="250" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A250" s="2"/>
     </row>
-    <row r="251" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A251" s="2"/>
     </row>
-    <row r="252" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A252" s="2"/>
     </row>
-    <row r="253" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A253" s="2"/>
     </row>
-    <row r="254" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A254" s="2"/>
     </row>
-    <row r="255" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A255" s="2"/>
     </row>
-    <row r="256" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A256" s="2"/>
     </row>
-    <row r="257" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A257" s="2"/>
     </row>
-    <row r="258" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A258" s="2"/>
     </row>
-    <row r="259" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A259" s="2"/>
     </row>
-    <row r="260" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A260" s="2"/>
     </row>
-    <row r="261" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A261" s="2"/>
     </row>
-    <row r="262" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A262" s="2"/>
     </row>
-    <row r="263" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A263" s="2"/>
     </row>
-    <row r="264" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A264" s="2"/>
     </row>
-    <row r="265" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A265" s="2"/>
     </row>
-    <row r="266" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A266" s="2"/>
     </row>
-    <row r="267" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A267" s="2"/>
     </row>
-    <row r="268" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A268" s="2"/>
     </row>
-    <row r="269" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A269" s="2"/>
     </row>
-    <row r="270" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A270" s="2"/>
     </row>
-    <row r="271" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A271" s="2"/>
     </row>
-    <row r="272" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A272" s="2"/>
     </row>
-    <row r="273" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A273" s="2"/>
     </row>
-    <row r="274" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A274" s="2"/>
     </row>
-    <row r="275" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A275" s="2"/>
     </row>
-    <row r="276" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A276" s="2"/>
     </row>
-    <row r="277" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A277" s="2"/>
     </row>
-    <row r="278" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A278" s="2"/>
     </row>
-    <row r="279" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A279" s="2"/>
     </row>
-    <row r="280" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A280" s="2"/>
     </row>
-    <row r="281" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A281" s="2"/>
     </row>
-    <row r="282" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A282" s="2"/>
     </row>
-    <row r="283" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A283" s="2"/>
     </row>
-    <row r="284" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A284" s="2"/>
     </row>
-    <row r="285" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A285" s="2"/>
     </row>
-    <row r="286" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A286" s="2"/>
     </row>
-    <row r="287" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A287" s="2"/>
     </row>
-    <row r="288" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A288" s="2"/>
     </row>
-    <row r="289" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A289" s="2"/>
     </row>
-    <row r="290" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A290" s="2"/>
     </row>
-    <row r="291" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A291" s="2"/>
     </row>
-    <row r="292" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A292" s="2"/>
     </row>
-    <row r="293" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A293" s="2"/>
     </row>
-    <row r="294" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A294" s="2"/>
     </row>
-    <row r="295" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A295" s="2"/>
     </row>
-    <row r="296" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A296" s="2"/>
     </row>
-    <row r="297" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A297" s="2"/>
     </row>
-    <row r="298" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A298" s="2"/>
     </row>
-    <row r="299" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A299" s="2"/>
     </row>
-    <row r="300" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A300" s="2"/>
     </row>
-    <row r="301" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A301" s="2"/>
     </row>
-    <row r="302" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A302" s="2"/>
     </row>
-    <row r="303" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A303" s="2"/>
     </row>
-    <row r="304" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A304" s="2"/>
     </row>
-    <row r="305" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A305" s="2"/>
     </row>
-    <row r="306" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A306" s="2"/>
     </row>
-    <row r="307" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A307" s="2"/>
     </row>
-    <row r="308" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A308" s="2"/>
     </row>
-    <row r="309" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A309" s="2"/>
     </row>
-    <row r="310" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A310" s="2"/>
     </row>
-    <row r="311" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A311" s="2"/>
     </row>
-    <row r="312" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A312" s="2"/>
     </row>
-    <row r="313" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A313" s="2"/>
     </row>
-    <row r="314" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A314" s="2"/>
     </row>
-    <row r="315" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A315" s="2"/>
     </row>
-    <row r="316" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A316" s="2"/>
     </row>
-    <row r="317" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A317" s="2"/>
     </row>
-    <row r="318" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A318" s="2"/>
     </row>
-    <row r="319" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A319" s="2"/>
     </row>
-    <row r="320" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A320" s="2"/>
     </row>
-    <row r="321" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A321" s="2"/>
     </row>
-    <row r="322" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A322" s="2"/>
     </row>
-    <row r="323" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A323" s="2"/>
     </row>
-    <row r="324" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A324" s="2"/>
     </row>
-    <row r="325" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A325" s="2"/>
     </row>
-    <row r="326" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A326" s="2"/>
     </row>
-    <row r="327" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A327" s="2"/>
     </row>
-    <row r="328" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A328" s="2"/>
     </row>
-    <row r="329" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A329" s="2"/>
     </row>
-    <row r="330" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A330" s="2"/>
     </row>
-    <row r="331" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A331" s="2"/>
     </row>
-    <row r="332" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A332" s="2"/>
     </row>
-    <row r="333" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A333" s="2"/>
     </row>
-    <row r="334" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A334" s="2"/>
     </row>
-    <row r="335" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A335" s="2"/>
     </row>
-    <row r="336" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A336" s="2"/>
     </row>
-    <row r="337" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A337" s="2"/>
     </row>
-    <row r="338" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A338" s="2"/>
     </row>
-    <row r="339" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A339" s="2"/>
     </row>
-    <row r="340" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A340" s="2"/>
     </row>
-    <row r="341" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A341" s="2"/>
     </row>
-    <row r="342" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A342" s="2"/>
     </row>
-    <row r="343" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A343" s="2"/>
     </row>
-    <row r="344" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A344" s="2"/>
     </row>
-    <row r="345" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A345" s="2"/>
     </row>
-    <row r="346" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A346" s="2"/>
     </row>
-    <row r="347" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A347" s="2"/>
     </row>
-    <row r="348" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A348" s="2"/>
     </row>
-    <row r="349" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A349" s="2"/>
     </row>
-    <row r="350" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A350" s="2"/>
     </row>
-    <row r="351" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A351" s="2"/>
     </row>
-    <row r="352" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A352" s="2"/>
     </row>
-    <row r="353" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A353" s="2"/>
     </row>
-    <row r="354" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A354" s="2"/>
     </row>
-    <row r="355" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A355" s="2"/>
     </row>
-    <row r="356" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A356" s="2"/>
     </row>
-    <row r="357" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A357" s="2"/>
     </row>
-    <row r="358" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A358" s="2"/>
     </row>
-    <row r="359" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A359" s="2"/>
     </row>
-    <row r="360" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A360" s="2"/>
     </row>
-    <row r="361" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A361" s="2"/>
     </row>
-    <row r="362" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A362" s="2"/>
     </row>
-    <row r="363" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A363" s="2"/>
     </row>
-    <row r="364" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A364" s="2"/>
     </row>
-    <row r="365" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A365" s="2"/>
     </row>
-    <row r="366" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A366" s="2"/>
     </row>
-    <row r="367" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A367" s="2"/>
     </row>
-    <row r="368" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A368" s="2"/>
     </row>
-    <row r="369" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A369" s="2"/>
     </row>
-    <row r="370" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A370" s="2"/>
     </row>
-    <row r="371" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A371" s="2"/>
     </row>
-    <row r="372" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A372" s="2"/>
     </row>
-    <row r="373" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A373" s="2"/>
     </row>
-    <row r="374" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A374" s="2"/>
     </row>
-    <row r="375" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A375" s="2"/>
     </row>
-    <row r="376" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A376" s="2"/>
     </row>
-    <row r="377" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A377" s="2"/>
     </row>
-    <row r="378" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A378" s="2"/>
     </row>
-    <row r="379" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A379" s="2"/>
     </row>
-    <row r="380" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A380" s="2"/>
     </row>
-    <row r="381" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A381" s="2"/>
     </row>
-    <row r="382" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A382" s="2"/>
     </row>
-    <row r="383" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A383" s="2"/>
     </row>
-    <row r="384" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A384" s="2"/>
     </row>
-    <row r="385" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A385" s="2"/>
     </row>
-    <row r="386" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A386" s="2"/>
     </row>
-    <row r="387" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A387" s="2"/>
     </row>
-    <row r="388" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A388" s="2"/>
     </row>
-    <row r="389" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A389" s="2"/>
     </row>
-    <row r="390" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A390" s="2"/>
     </row>
-    <row r="391" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A391" s="2"/>
     </row>
-    <row r="392" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A392" s="2"/>
     </row>
-    <row r="393" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A393" s="2"/>
     </row>
-    <row r="394" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A394" s="2"/>
     </row>
-    <row r="395" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A395" s="2"/>
     </row>
-    <row r="396" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A396" s="2"/>
     </row>
-    <row r="397" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A397" s="2"/>
     </row>
-    <row r="398" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A398" s="2"/>
     </row>
-    <row r="399" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A399" s="2"/>
     </row>
-    <row r="400" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A400" s="2"/>
     </row>
-    <row r="401" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A401" s="2"/>
     </row>
-    <row r="402" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A402" s="2"/>
     </row>
-    <row r="403" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A403" s="2"/>
     </row>
-    <row r="404" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A404" s="2"/>
     </row>
-    <row r="405" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A405" s="2"/>
     </row>
-    <row r="406" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A406" s="2"/>
     </row>
-    <row r="407" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A407" s="2"/>
     </row>
-    <row r="408" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A408" s="2"/>
     </row>
-    <row r="409" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A409" s="2"/>
     </row>
-    <row r="410" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A410" s="2"/>
     </row>
-    <row r="411" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A411" s="2"/>
     </row>
-    <row r="412" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A412" s="2"/>
     </row>
-    <row r="413" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A413" s="2"/>
     </row>
-    <row r="414" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A414" s="2"/>
     </row>
-    <row r="415" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A415" s="2"/>
     </row>
-    <row r="416" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A416" s="2"/>
     </row>
-    <row r="417" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A417" s="2"/>
     </row>
-    <row r="418" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A418" s="2"/>
     </row>
-    <row r="419" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A419" s="2"/>
     </row>
-    <row r="420" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A420" s="2"/>
     </row>
-    <row r="421" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A421" s="2"/>
     </row>
-    <row r="422" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A422" s="2"/>
     </row>
-    <row r="423" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A423" s="2"/>
     </row>
-    <row r="424" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A424" s="2"/>
     </row>
-    <row r="425" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A425" s="2"/>
     </row>
-    <row r="426" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A426" s="2"/>
     </row>
-    <row r="427" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A427" s="2"/>
     </row>
-    <row r="428" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A428" s="2"/>
     </row>
-    <row r="429" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A429" s="2"/>
     </row>
-    <row r="430" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A430" s="2"/>
     </row>
-    <row r="431" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A431" s="2"/>
     </row>
-    <row r="432" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A432" s="2"/>
     </row>
-    <row r="433" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A433" s="2"/>
     </row>
-    <row r="434" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A434" s="2"/>
     </row>
-    <row r="435" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A435" s="2"/>
     </row>
-    <row r="436" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A436" s="2"/>
     </row>
-    <row r="437" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A437" s="2"/>
     </row>
-    <row r="438" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A438" s="2"/>
     </row>
   </sheetData>
@@ -14112,27 +14108,27 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="35.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" customWidth="1"/>
     <col min="4" max="4" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="40" t="s">
+      <c r="C1" s="40"/>
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>17</v>
       </c>
@@ -14142,9 +14138,9 @@
       <c r="C2" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="40"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D2" s="41"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="e" cm="1" vm="2">
         <f t="array" ref="A3">_xlfn.CHOOSEROWS(
     IF('FILL ME'!B9="Bottle Number", 'Label IDs'!J:J, 'Label IDs'!K:K),
@@ -14156,577 +14152,577 @@
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="21"/>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="21"/>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="21"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
       <c r="D13" s="21"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
     </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="21"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="21"/>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
       <c r="D23" s="21"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
     </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="21"/>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
       <c r="D25" s="21"/>
     </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
     </row>
-    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="21"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
     </row>
-    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
     </row>
-    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="21"/>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
     </row>
-    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
     </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="21"/>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
     </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
     </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="21"/>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
     </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
     </row>
-    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
     </row>
-    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
     </row>
-    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="21"/>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
       <c r="D37" s="21"/>
     </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
     </row>
-    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="21"/>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
     </row>
-    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
     </row>
-    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="21"/>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
     </row>
-    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
     </row>
-    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="21"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
     </row>
-    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
     </row>
-    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
     </row>
-    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
     </row>
-    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
     </row>
-    <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
     </row>
-    <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
     </row>
-    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
     </row>
-    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
     </row>
-    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
     </row>
-    <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
     </row>
-    <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
     </row>
-    <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
     </row>
-    <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
     </row>
-    <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="9"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
     </row>
-    <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
     </row>
-    <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="9"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
     </row>
-    <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
     </row>
-    <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="9"/>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
     </row>
-    <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="21"/>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
     </row>
-    <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="9"/>
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
     </row>
-    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="21"/>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
     </row>
-    <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="9"/>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
     </row>
-    <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
     </row>
-    <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="9"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
     </row>
-    <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="21"/>
       <c r="B69" s="21"/>
       <c r="C69" s="21"/>
       <c r="D69" s="21"/>
     </row>
-    <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="9"/>
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
     </row>
-    <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="21"/>
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
     </row>
-    <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
     </row>
-    <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="21"/>
       <c r="B73" s="21"/>
       <c r="C73" s="21"/>
       <c r="D73" s="21"/>
     </row>
-    <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
     </row>
-    <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
     </row>
-    <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="9"/>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
     </row>
-    <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="21"/>
       <c r="B77" s="21"/>
       <c r="C77" s="21"/>
       <c r="D77" s="21"/>
     </row>
-    <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="9"/>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
     </row>
-    <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="21"/>
       <c r="B79" s="21"/>
       <c r="C79" s="21"/>
       <c r="D79" s="21"/>
     </row>
-    <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="9"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
     </row>
-    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="21"/>
       <c r="B81" s="21"/>
       <c r="C81" s="21"/>
       <c r="D81" s="21"/>
     </row>
-    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="9"/>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
     </row>
-    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
     </row>
-    <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="9"/>
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
     </row>
-    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="21"/>
       <c r="B85" s="21"/>
       <c r="C85" s="21"/>
       <c r="D85" s="21"/>
     </row>
-    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="9"/>
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
     </row>
-    <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="21"/>
       <c r="B87" s="21"/>
       <c r="C87" s="21"/>
       <c r="D87" s="21"/>
     </row>
-    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="9"/>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
     </row>
-    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="21"/>
       <c r="B89" s="21"/>
       <c r="C89" s="21"/>
       <c r="D89" s="21"/>
     </row>
-    <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="9"/>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
     </row>
-    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
     </row>
-    <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="9"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
     </row>
-    <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="21"/>
       <c r="B93" s="21"/>
       <c r="C93" s="21"/>
       <c r="D93" s="21"/>
     </row>
-    <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="9"/>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
     </row>
-    <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="21"/>
       <c r="B95" s="21"/>
       <c r="C95" s="21"/>
       <c r="D95" s="21"/>
     </row>
-    <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="9"/>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
     </row>
-    <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="21"/>
       <c r="B97" s="21"/>
       <c r="C97" s="21"/>
       <c r="D97" s="21"/>
     </row>
-    <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="9"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
     </row>
-    <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="21"/>
       <c r="B99" s="21"/>
       <c r="C99" s="21"/>
@@ -14753,27 +14749,27 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.28515625" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="35.26953125" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" customWidth="1"/>
+    <col min="3" max="3" width="16.54296875" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="40" t="s">
+      <c r="C1" s="40"/>
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>17</v>
       </c>
@@ -14783,9 +14779,9 @@
       <c r="C2" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="40"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D2" s="41"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="e" cm="1" vm="2">
         <f t="array" ref="A3">_xlfn.CHOOSEROWS(
     IF('FILL ME'!B9="Bottle Number", 'Label IDs'!J:J, 'Label IDs'!K:K),
@@ -14797,577 +14793,577 @@
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="21"/>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="21"/>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="21"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
       <c r="D13" s="21"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
     </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="21"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="21"/>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
       <c r="D23" s="21"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
     </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="21"/>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
       <c r="D25" s="21"/>
     </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
     </row>
-    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="21"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
     </row>
-    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
     </row>
-    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="21"/>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
     </row>
-    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
     </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="21"/>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
     </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
     </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="21"/>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
     </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
     </row>
-    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
     </row>
-    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
     </row>
-    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="21"/>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
       <c r="D37" s="21"/>
     </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
     </row>
-    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="21"/>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
     </row>
-    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
     </row>
-    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="21"/>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
     </row>
-    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
     </row>
-    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="21"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
     </row>
-    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
     </row>
-    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
     </row>
-    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
     </row>
-    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
     </row>
-    <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
     </row>
-    <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
     </row>
-    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
     </row>
-    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
     </row>
-    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
     </row>
-    <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
     </row>
-    <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
     </row>
-    <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
     </row>
-    <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
     </row>
-    <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="9"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
     </row>
-    <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
     </row>
-    <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="9"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
     </row>
-    <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
     </row>
-    <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="9"/>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
     </row>
-    <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="21"/>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
     </row>
-    <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="9"/>
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
     </row>
-    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="21"/>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
     </row>
-    <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="9"/>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
     </row>
-    <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
     </row>
-    <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="9"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
     </row>
-    <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="21"/>
       <c r="B69" s="21"/>
       <c r="C69" s="21"/>
       <c r="D69" s="21"/>
     </row>
-    <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="9"/>
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
     </row>
-    <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="21"/>
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
     </row>
-    <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
     </row>
-    <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="21"/>
       <c r="B73" s="21"/>
       <c r="C73" s="21"/>
       <c r="D73" s="21"/>
     </row>
-    <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
     </row>
-    <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
     </row>
-    <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="9"/>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
     </row>
-    <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="21"/>
       <c r="B77" s="21"/>
       <c r="C77" s="21"/>
       <c r="D77" s="21"/>
     </row>
-    <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="9"/>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
     </row>
-    <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="21"/>
       <c r="B79" s="21"/>
       <c r="C79" s="21"/>
       <c r="D79" s="21"/>
     </row>
-    <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="9"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
     </row>
-    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="21"/>
       <c r="B81" s="21"/>
       <c r="C81" s="21"/>
       <c r="D81" s="21"/>
     </row>
-    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="9"/>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
     </row>
-    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
     </row>
-    <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="9"/>
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
     </row>
-    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="21"/>
       <c r="B85" s="21"/>
       <c r="C85" s="21"/>
       <c r="D85" s="21"/>
     </row>
-    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="9"/>
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
     </row>
-    <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="21"/>
       <c r="B87" s="21"/>
       <c r="C87" s="21"/>
       <c r="D87" s="21"/>
     </row>
-    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="9"/>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
     </row>
-    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="21"/>
       <c r="B89" s="21"/>
       <c r="C89" s="21"/>
       <c r="D89" s="21"/>
     </row>
-    <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="9"/>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
     </row>
-    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
     </row>
-    <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="9"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
     </row>
-    <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="21"/>
       <c r="B93" s="21"/>
       <c r="C93" s="21"/>
       <c r="D93" s="21"/>
     </row>
-    <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="9"/>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
     </row>
-    <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="21"/>
       <c r="B95" s="21"/>
       <c r="C95" s="21"/>
       <c r="D95" s="21"/>
     </row>
-    <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="9"/>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
     </row>
-    <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="21"/>
       <c r="B97" s="21"/>
       <c r="C97" s="21"/>
       <c r="D97" s="21"/>
     </row>
-    <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="9"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
       <c r="D98" s="9"/>
     </row>
-    <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="21"/>
       <c r="B99" s="21"/>
       <c r="C99" s="21"/>
